--- a/excel-templates/稼働確認_RISE_テンプレート.xlsx
+++ b/excel-templates/稼働確認_RISE_テンプレート.xlsx
@@ -10,7 +10,7 @@
     <sheet name="稼働確認" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'稼働確認'!$A$2:$P$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'稼働確認'!$A$2:$Q$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -526,17 +526,18 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -574,55 +575,60 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>人員</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>開始</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>終了</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>休憩(分)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>実働時間</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>作業内容</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>高速料金</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>移動距離</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>燃料費</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>駐車場</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>資材費</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>経費合計</t>
         </is>
@@ -637,24 +643,25 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="6" t="n"/>
+      <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="7">
-        <f>IF(F3="","",MAX(0,(G3-F3)*24-H3/60))</f>
-        <v/>
-      </c>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="8" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="7">
+        <f>IF(G3="","",MAX(0,(H3-G3)*24-I3/60))</f>
+        <v/>
+      </c>
+      <c r="K3" s="5" t="n"/>
       <c r="L3" s="8" t="n"/>
-      <c r="M3" s="8">
-        <f>IF(L3="","",L3*20)</f>
-        <v/>
-      </c>
-      <c r="N3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8">
+        <f>IF(M3="","",M3*20)</f>
+        <v/>
+      </c>
       <c r="O3" s="8" t="n"/>
-      <c r="P3" s="8">
-        <f>IF(D3="","",SUM(K3,M3,N3,O3))</f>
+      <c r="P3" s="8" t="n"/>
+      <c r="Q3" s="8">
+        <f>IF(D3="","",SUM(L3,N3,O3,P3))</f>
         <v/>
       </c>
     </row>
@@ -667,24 +674,25 @@
       <c r="C4" s="11" t="n"/>
       <c r="D4" s="11" t="n"/>
       <c r="E4" s="11" t="n"/>
-      <c r="F4" s="12" t="n"/>
+      <c r="F4" s="11" t="n"/>
       <c r="G4" s="12" t="n"/>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="13">
-        <f>IF(F4="","",MAX(0,(G4-F4)*24-H4/60))</f>
-        <v/>
-      </c>
-      <c r="J4" s="11" t="n"/>
-      <c r="K4" s="14" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="13">
+        <f>IF(G4="","",MAX(0,(H4-G4)*24-I4/60))</f>
+        <v/>
+      </c>
+      <c r="K4" s="11" t="n"/>
       <c r="L4" s="14" t="n"/>
-      <c r="M4" s="14">
-        <f>IF(L4="","",L4*20)</f>
-        <v/>
-      </c>
-      <c r="N4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14">
+        <f>IF(M4="","",M4*20)</f>
+        <v/>
+      </c>
       <c r="O4" s="14" t="n"/>
-      <c r="P4" s="14">
-        <f>IF(D4="","",SUM(K4,M4,N4,O4))</f>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14">
+        <f>IF(D4="","",SUM(L4,N4,O4,P4))</f>
         <v/>
       </c>
     </row>
@@ -697,24 +705,25 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="7">
-        <f>IF(F5="","",MAX(0,(G5-F5)*24-H5/60))</f>
-        <v/>
-      </c>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="8" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="7">
+        <f>IF(G5="","",MAX(0,(H5-G5)*24-I5/60))</f>
+        <v/>
+      </c>
+      <c r="K5" s="5" t="n"/>
       <c r="L5" s="8" t="n"/>
-      <c r="M5" s="8">
-        <f>IF(L5="","",L5*20)</f>
-        <v/>
-      </c>
-      <c r="N5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="8">
+        <f>IF(M5="","",M5*20)</f>
+        <v/>
+      </c>
       <c r="O5" s="8" t="n"/>
-      <c r="P5" s="8">
-        <f>IF(D5="","",SUM(K5,M5,N5,O5))</f>
+      <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="8">
+        <f>IF(D5="","",SUM(L5,N5,O5,P5))</f>
         <v/>
       </c>
     </row>
@@ -727,24 +736,25 @@
       <c r="C6" s="11" t="n"/>
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n"/>
-      <c r="F6" s="12" t="n"/>
+      <c r="F6" s="11" t="n"/>
       <c r="G6" s="12" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="13">
-        <f>IF(F6="","",MAX(0,(G6-F6)*24-H6/60))</f>
-        <v/>
-      </c>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="14" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="13">
+        <f>IF(G6="","",MAX(0,(H6-G6)*24-I6/60))</f>
+        <v/>
+      </c>
+      <c r="K6" s="11" t="n"/>
       <c r="L6" s="14" t="n"/>
-      <c r="M6" s="14">
-        <f>IF(L6="","",L6*20)</f>
-        <v/>
-      </c>
-      <c r="N6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14">
+        <f>IF(M6="","",M6*20)</f>
+        <v/>
+      </c>
       <c r="O6" s="14" t="n"/>
-      <c r="P6" s="14">
-        <f>IF(D6="","",SUM(K6,M6,N6,O6))</f>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14">
+        <f>IF(D6="","",SUM(L6,N6,O6,P6))</f>
         <v/>
       </c>
     </row>
@@ -757,24 +767,25 @@
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="6" t="n"/>
+      <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="7">
-        <f>IF(F7="","",MAX(0,(G7-F7)*24-H7/60))</f>
-        <v/>
-      </c>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="8" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="7">
+        <f>IF(G7="","",MAX(0,(H7-G7)*24-I7/60))</f>
+        <v/>
+      </c>
+      <c r="K7" s="5" t="n"/>
       <c r="L7" s="8" t="n"/>
-      <c r="M7" s="8">
-        <f>IF(L7="","",L7*20)</f>
-        <v/>
-      </c>
-      <c r="N7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8">
+        <f>IF(M7="","",M7*20)</f>
+        <v/>
+      </c>
       <c r="O7" s="8" t="n"/>
-      <c r="P7" s="8">
-        <f>IF(D7="","",SUM(K7,M7,N7,O7))</f>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8">
+        <f>IF(D7="","",SUM(L7,N7,O7,P7))</f>
         <v/>
       </c>
     </row>
@@ -787,24 +798,25 @@
       <c r="C8" s="11" t="n"/>
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="11" t="n"/>
-      <c r="F8" s="12" t="n"/>
+      <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="13">
-        <f>IF(F8="","",MAX(0,(G8-F8)*24-H8/60))</f>
-        <v/>
-      </c>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="14" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="13">
+        <f>IF(G8="","",MAX(0,(H8-G8)*24-I8/60))</f>
+        <v/>
+      </c>
+      <c r="K8" s="11" t="n"/>
       <c r="L8" s="14" t="n"/>
-      <c r="M8" s="14">
-        <f>IF(L8="","",L8*20)</f>
-        <v/>
-      </c>
-      <c r="N8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14">
+        <f>IF(M8="","",M8*20)</f>
+        <v/>
+      </c>
       <c r="O8" s="14" t="n"/>
-      <c r="P8" s="14">
-        <f>IF(D8="","",SUM(K8,M8,N8,O8))</f>
+      <c r="P8" s="14" t="n"/>
+      <c r="Q8" s="14">
+        <f>IF(D8="","",SUM(L8,N8,O8,P8))</f>
         <v/>
       </c>
     </row>
@@ -817,24 +829,25 @@
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="7">
-        <f>IF(F9="","",MAX(0,(G9-F9)*24-H9/60))</f>
-        <v/>
-      </c>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="8" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="7">
+        <f>IF(G9="","",MAX(0,(H9-G9)*24-I9/60))</f>
+        <v/>
+      </c>
+      <c r="K9" s="5" t="n"/>
       <c r="L9" s="8" t="n"/>
-      <c r="M9" s="8">
-        <f>IF(L9="","",L9*20)</f>
-        <v/>
-      </c>
-      <c r="N9" s="8" t="n"/>
+      <c r="M9" s="8" t="n"/>
+      <c r="N9" s="8">
+        <f>IF(M9="","",M9*20)</f>
+        <v/>
+      </c>
       <c r="O9" s="8" t="n"/>
-      <c r="P9" s="8">
-        <f>IF(D9="","",SUM(K9,M9,N9,O9))</f>
+      <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="8">
+        <f>IF(D9="","",SUM(L9,N9,O9,P9))</f>
         <v/>
       </c>
     </row>
@@ -847,24 +860,25 @@
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="11" t="n"/>
       <c r="E10" s="11" t="n"/>
-      <c r="F10" s="12" t="n"/>
+      <c r="F10" s="11" t="n"/>
       <c r="G10" s="12" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="13">
-        <f>IF(F10="","",MAX(0,(G10-F10)*24-H10/60))</f>
-        <v/>
-      </c>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="14" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="13">
+        <f>IF(G10="","",MAX(0,(H10-G10)*24-I10/60))</f>
+        <v/>
+      </c>
+      <c r="K10" s="11" t="n"/>
       <c r="L10" s="14" t="n"/>
-      <c r="M10" s="14">
-        <f>IF(L10="","",L10*20)</f>
-        <v/>
-      </c>
-      <c r="N10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
+      <c r="N10" s="14">
+        <f>IF(M10="","",M10*20)</f>
+        <v/>
+      </c>
       <c r="O10" s="14" t="n"/>
-      <c r="P10" s="14">
-        <f>IF(D10="","",SUM(K10,M10,N10,O10))</f>
+      <c r="P10" s="14" t="n"/>
+      <c r="Q10" s="14">
+        <f>IF(D10="","",SUM(L10,N10,O10,P10))</f>
         <v/>
       </c>
     </row>
@@ -877,24 +891,25 @@
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
-      <c r="F11" s="6" t="n"/>
+      <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="7">
-        <f>IF(F11="","",MAX(0,(G11-F11)*24-H11/60))</f>
-        <v/>
-      </c>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="8" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="7">
+        <f>IF(G11="","",MAX(0,(H11-G11)*24-I11/60))</f>
+        <v/>
+      </c>
+      <c r="K11" s="5" t="n"/>
       <c r="L11" s="8" t="n"/>
-      <c r="M11" s="8">
-        <f>IF(L11="","",L11*20)</f>
-        <v/>
-      </c>
-      <c r="N11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8">
+        <f>IF(M11="","",M11*20)</f>
+        <v/>
+      </c>
       <c r="O11" s="8" t="n"/>
-      <c r="P11" s="8">
-        <f>IF(D11="","",SUM(K11,M11,N11,O11))</f>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8">
+        <f>IF(D11="","",SUM(L11,N11,O11,P11))</f>
         <v/>
       </c>
     </row>
@@ -907,24 +922,25 @@
       <c r="C12" s="11" t="n"/>
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="12" t="n"/>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="12" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="13">
-        <f>IF(F12="","",MAX(0,(G12-F12)*24-H12/60))</f>
-        <v/>
-      </c>
-      <c r="J12" s="11" t="n"/>
-      <c r="K12" s="14" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="13">
+        <f>IF(G12="","",MAX(0,(H12-G12)*24-I12/60))</f>
+        <v/>
+      </c>
+      <c r="K12" s="11" t="n"/>
       <c r="L12" s="14" t="n"/>
-      <c r="M12" s="14">
-        <f>IF(L12="","",L12*20)</f>
-        <v/>
-      </c>
-      <c r="N12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
+      <c r="N12" s="14">
+        <f>IF(M12="","",M12*20)</f>
+        <v/>
+      </c>
       <c r="O12" s="14" t="n"/>
-      <c r="P12" s="14">
-        <f>IF(D12="","",SUM(K12,M12,N12,O12))</f>
+      <c r="P12" s="14" t="n"/>
+      <c r="Q12" s="14">
+        <f>IF(D12="","",SUM(L12,N12,O12,P12))</f>
         <v/>
       </c>
     </row>
@@ -937,24 +953,25 @@
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="6" t="n"/>
+      <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="7">
-        <f>IF(F13="","",MAX(0,(G13-F13)*24-H13/60))</f>
-        <v/>
-      </c>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="8" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="7">
+        <f>IF(G13="","",MAX(0,(H13-G13)*24-I13/60))</f>
+        <v/>
+      </c>
+      <c r="K13" s="5" t="n"/>
       <c r="L13" s="8" t="n"/>
-      <c r="M13" s="8">
-        <f>IF(L13="","",L13*20)</f>
-        <v/>
-      </c>
-      <c r="N13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8">
+        <f>IF(M13="","",M13*20)</f>
+        <v/>
+      </c>
       <c r="O13" s="8" t="n"/>
-      <c r="P13" s="8">
-        <f>IF(D13="","",SUM(K13,M13,N13,O13))</f>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8">
+        <f>IF(D13="","",SUM(L13,N13,O13,P13))</f>
         <v/>
       </c>
     </row>
@@ -967,24 +984,25 @@
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="11" t="n"/>
-      <c r="F14" s="12" t="n"/>
+      <c r="F14" s="11" t="n"/>
       <c r="G14" s="12" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="13">
-        <f>IF(F14="","",MAX(0,(G14-F14)*24-H14/60))</f>
-        <v/>
-      </c>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="14" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="13">
+        <f>IF(G14="","",MAX(0,(H14-G14)*24-I14/60))</f>
+        <v/>
+      </c>
+      <c r="K14" s="11" t="n"/>
       <c r="L14" s="14" t="n"/>
-      <c r="M14" s="14">
-        <f>IF(L14="","",L14*20)</f>
-        <v/>
-      </c>
-      <c r="N14" s="14" t="n"/>
+      <c r="M14" s="14" t="n"/>
+      <c r="N14" s="14">
+        <f>IF(M14="","",M14*20)</f>
+        <v/>
+      </c>
       <c r="O14" s="14" t="n"/>
-      <c r="P14" s="14">
-        <f>IF(D14="","",SUM(K14,M14,N14,O14))</f>
+      <c r="P14" s="14" t="n"/>
+      <c r="Q14" s="14">
+        <f>IF(D14="","",SUM(L14,N14,O14,P14))</f>
         <v/>
       </c>
     </row>
@@ -997,24 +1015,25 @@
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
-      <c r="F15" s="6" t="n"/>
+      <c r="F15" s="5" t="n"/>
       <c r="G15" s="6" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="7">
-        <f>IF(F15="","",MAX(0,(G15-F15)*24-H15/60))</f>
-        <v/>
-      </c>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="8" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="7">
+        <f>IF(G15="","",MAX(0,(H15-G15)*24-I15/60))</f>
+        <v/>
+      </c>
+      <c r="K15" s="5" t="n"/>
       <c r="L15" s="8" t="n"/>
-      <c r="M15" s="8">
-        <f>IF(L15="","",L15*20)</f>
-        <v/>
-      </c>
-      <c r="N15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
+      <c r="N15" s="8">
+        <f>IF(M15="","",M15*20)</f>
+        <v/>
+      </c>
       <c r="O15" s="8" t="n"/>
-      <c r="P15" s="8">
-        <f>IF(D15="","",SUM(K15,M15,N15,O15))</f>
+      <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="8">
+        <f>IF(D15="","",SUM(L15,N15,O15,P15))</f>
         <v/>
       </c>
     </row>
@@ -1027,24 +1046,25 @@
       <c r="C16" s="11" t="n"/>
       <c r="D16" s="11" t="n"/>
       <c r="E16" s="11" t="n"/>
-      <c r="F16" s="12" t="n"/>
+      <c r="F16" s="11" t="n"/>
       <c r="G16" s="12" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="13">
-        <f>IF(F16="","",MAX(0,(G16-F16)*24-H16/60))</f>
-        <v/>
-      </c>
-      <c r="J16" s="11" t="n"/>
-      <c r="K16" s="14" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="13">
+        <f>IF(G16="","",MAX(0,(H16-G16)*24-I16/60))</f>
+        <v/>
+      </c>
+      <c r="K16" s="11" t="n"/>
       <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14">
-        <f>IF(L16="","",L16*20)</f>
-        <v/>
-      </c>
-      <c r="N16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14">
+        <f>IF(M16="","",M16*20)</f>
+        <v/>
+      </c>
       <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14">
-        <f>IF(D16="","",SUM(K16,M16,N16,O16))</f>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14">
+        <f>IF(D16="","",SUM(L16,N16,O16,P16))</f>
         <v/>
       </c>
     </row>
@@ -1057,24 +1077,25 @@
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="6" t="n"/>
+      <c r="F17" s="5" t="n"/>
       <c r="G17" s="6" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="7">
-        <f>IF(F17="","",MAX(0,(G17-F17)*24-H17/60))</f>
-        <v/>
-      </c>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="8" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="7">
+        <f>IF(G17="","",MAX(0,(H17-G17)*24-I17/60))</f>
+        <v/>
+      </c>
+      <c r="K17" s="5" t="n"/>
       <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8">
-        <f>IF(L17="","",L17*20)</f>
-        <v/>
-      </c>
-      <c r="N17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8">
+        <f>IF(M17="","",M17*20)</f>
+        <v/>
+      </c>
       <c r="O17" s="8" t="n"/>
-      <c r="P17" s="8">
-        <f>IF(D17="","",SUM(K17,M17,N17,O17))</f>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8">
+        <f>IF(D17="","",SUM(L17,N17,O17,P17))</f>
         <v/>
       </c>
     </row>
@@ -1087,24 +1108,25 @@
       <c r="C18" s="11" t="n"/>
       <c r="D18" s="11" t="n"/>
       <c r="E18" s="11" t="n"/>
-      <c r="F18" s="12" t="n"/>
+      <c r="F18" s="11" t="n"/>
       <c r="G18" s="12" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="13">
-        <f>IF(F18="","",MAX(0,(G18-F18)*24-H18/60))</f>
-        <v/>
-      </c>
-      <c r="J18" s="11" t="n"/>
-      <c r="K18" s="14" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="13">
+        <f>IF(G18="","",MAX(0,(H18-G18)*24-I18/60))</f>
+        <v/>
+      </c>
+      <c r="K18" s="11" t="n"/>
       <c r="L18" s="14" t="n"/>
-      <c r="M18" s="14">
-        <f>IF(L18="","",L18*20)</f>
-        <v/>
-      </c>
-      <c r="N18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14">
+        <f>IF(M18="","",M18*20)</f>
+        <v/>
+      </c>
       <c r="O18" s="14" t="n"/>
-      <c r="P18" s="14">
-        <f>IF(D18="","",SUM(K18,M18,N18,O18))</f>
+      <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14">
+        <f>IF(D18="","",SUM(L18,N18,O18,P18))</f>
         <v/>
       </c>
     </row>
@@ -1117,24 +1139,25 @@
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
-      <c r="F19" s="6" t="n"/>
+      <c r="F19" s="5" t="n"/>
       <c r="G19" s="6" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="7">
-        <f>IF(F19="","",MAX(0,(G19-F19)*24-H19/60))</f>
-        <v/>
-      </c>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="8" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="7">
+        <f>IF(G19="","",MAX(0,(H19-G19)*24-I19/60))</f>
+        <v/>
+      </c>
+      <c r="K19" s="5" t="n"/>
       <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8">
-        <f>IF(L19="","",L19*20)</f>
-        <v/>
-      </c>
-      <c r="N19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8">
+        <f>IF(M19="","",M19*20)</f>
+        <v/>
+      </c>
       <c r="O19" s="8" t="n"/>
-      <c r="P19" s="8">
-        <f>IF(D19="","",SUM(K19,M19,N19,O19))</f>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8">
+        <f>IF(D19="","",SUM(L19,N19,O19,P19))</f>
         <v/>
       </c>
     </row>
@@ -1147,24 +1170,25 @@
       <c r="C20" s="11" t="n"/>
       <c r="D20" s="11" t="n"/>
       <c r="E20" s="11" t="n"/>
-      <c r="F20" s="12" t="n"/>
+      <c r="F20" s="11" t="n"/>
       <c r="G20" s="12" t="n"/>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="13">
-        <f>IF(F20="","",MAX(0,(G20-F20)*24-H20/60))</f>
-        <v/>
-      </c>
-      <c r="J20" s="11" t="n"/>
-      <c r="K20" s="14" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="13">
+        <f>IF(G20="","",MAX(0,(H20-G20)*24-I20/60))</f>
+        <v/>
+      </c>
+      <c r="K20" s="11" t="n"/>
       <c r="L20" s="14" t="n"/>
-      <c r="M20" s="14">
-        <f>IF(L20="","",L20*20)</f>
-        <v/>
-      </c>
-      <c r="N20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14">
+        <f>IF(M20="","",M20*20)</f>
+        <v/>
+      </c>
       <c r="O20" s="14" t="n"/>
-      <c r="P20" s="14">
-        <f>IF(D20="","",SUM(K20,M20,N20,O20))</f>
+      <c r="P20" s="14" t="n"/>
+      <c r="Q20" s="14">
+        <f>IF(D20="","",SUM(L20,N20,O20,P20))</f>
         <v/>
       </c>
     </row>
@@ -1177,24 +1201,25 @@
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
-      <c r="F21" s="6" t="n"/>
+      <c r="F21" s="5" t="n"/>
       <c r="G21" s="6" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="7">
-        <f>IF(F21="","",MAX(0,(G21-F21)*24-H21/60))</f>
-        <v/>
-      </c>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="8" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="7">
+        <f>IF(G21="","",MAX(0,(H21-G21)*24-I21/60))</f>
+        <v/>
+      </c>
+      <c r="K21" s="5" t="n"/>
       <c r="L21" s="8" t="n"/>
-      <c r="M21" s="8">
-        <f>IF(L21="","",L21*20)</f>
-        <v/>
-      </c>
-      <c r="N21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="8">
+        <f>IF(M21="","",M21*20)</f>
+        <v/>
+      </c>
       <c r="O21" s="8" t="n"/>
-      <c r="P21" s="8">
-        <f>IF(D21="","",SUM(K21,M21,N21,O21))</f>
+      <c r="P21" s="8" t="n"/>
+      <c r="Q21" s="8">
+        <f>IF(D21="","",SUM(L21,N21,O21,P21))</f>
         <v/>
       </c>
     </row>
@@ -1207,24 +1232,25 @@
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="11" t="n"/>
       <c r="E22" s="11" t="n"/>
-      <c r="F22" s="12" t="n"/>
+      <c r="F22" s="11" t="n"/>
       <c r="G22" s="12" t="n"/>
-      <c r="H22" s="11" t="n"/>
-      <c r="I22" s="13">
-        <f>IF(F22="","",MAX(0,(G22-F22)*24-H22/60))</f>
-        <v/>
-      </c>
-      <c r="J22" s="11" t="n"/>
-      <c r="K22" s="14" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="13">
+        <f>IF(G22="","",MAX(0,(H22-G22)*24-I22/60))</f>
+        <v/>
+      </c>
+      <c r="K22" s="11" t="n"/>
       <c r="L22" s="14" t="n"/>
-      <c r="M22" s="14">
-        <f>IF(L22="","",L22*20)</f>
-        <v/>
-      </c>
-      <c r="N22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+      <c r="N22" s="14">
+        <f>IF(M22="","",M22*20)</f>
+        <v/>
+      </c>
       <c r="O22" s="14" t="n"/>
-      <c r="P22" s="14">
-        <f>IF(D22="","",SUM(K22,M22,N22,O22))</f>
+      <c r="P22" s="14" t="n"/>
+      <c r="Q22" s="14">
+        <f>IF(D22="","",SUM(L22,N22,O22,P22))</f>
         <v/>
       </c>
     </row>
@@ -1237,24 +1263,25 @@
       <c r="C23" s="5" t="n"/>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
-      <c r="F23" s="6" t="n"/>
+      <c r="F23" s="5" t="n"/>
       <c r="G23" s="6" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="7">
-        <f>IF(F23="","",MAX(0,(G23-F23)*24-H23/60))</f>
-        <v/>
-      </c>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="8" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="7">
+        <f>IF(G23="","",MAX(0,(H23-G23)*24-I23/60))</f>
+        <v/>
+      </c>
+      <c r="K23" s="5" t="n"/>
       <c r="L23" s="8" t="n"/>
-      <c r="M23" s="8">
-        <f>IF(L23="","",L23*20)</f>
-        <v/>
-      </c>
-      <c r="N23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="8">
+        <f>IF(M23="","",M23*20)</f>
+        <v/>
+      </c>
       <c r="O23" s="8" t="n"/>
-      <c r="P23" s="8">
-        <f>IF(D23="","",SUM(K23,M23,N23,O23))</f>
+      <c r="P23" s="8" t="n"/>
+      <c r="Q23" s="8">
+        <f>IF(D23="","",SUM(L23,N23,O23,P23))</f>
         <v/>
       </c>
     </row>
@@ -1267,24 +1294,25 @@
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="11" t="n"/>
       <c r="E24" s="11" t="n"/>
-      <c r="F24" s="12" t="n"/>
+      <c r="F24" s="11" t="n"/>
       <c r="G24" s="12" t="n"/>
-      <c r="H24" s="11" t="n"/>
-      <c r="I24" s="13">
-        <f>IF(F24="","",MAX(0,(G24-F24)*24-H24/60))</f>
-        <v/>
-      </c>
-      <c r="J24" s="11" t="n"/>
-      <c r="K24" s="14" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="13">
+        <f>IF(G24="","",MAX(0,(H24-G24)*24-I24/60))</f>
+        <v/>
+      </c>
+      <c r="K24" s="11" t="n"/>
       <c r="L24" s="14" t="n"/>
-      <c r="M24" s="14">
-        <f>IF(L24="","",L24*20)</f>
-        <v/>
-      </c>
-      <c r="N24" s="14" t="n"/>
+      <c r="M24" s="14" t="n"/>
+      <c r="N24" s="14">
+        <f>IF(M24="","",M24*20)</f>
+        <v/>
+      </c>
       <c r="O24" s="14" t="n"/>
-      <c r="P24" s="14">
-        <f>IF(D24="","",SUM(K24,M24,N24,O24))</f>
+      <c r="P24" s="14" t="n"/>
+      <c r="Q24" s="14">
+        <f>IF(D24="","",SUM(L24,N24,O24,P24))</f>
         <v/>
       </c>
     </row>
@@ -1297,24 +1325,25 @@
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
-      <c r="F25" s="6" t="n"/>
+      <c r="F25" s="5" t="n"/>
       <c r="G25" s="6" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="7">
-        <f>IF(F25="","",MAX(0,(G25-F25)*24-H25/60))</f>
-        <v/>
-      </c>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="8" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="7">
+        <f>IF(G25="","",MAX(0,(H25-G25)*24-I25/60))</f>
+        <v/>
+      </c>
+      <c r="K25" s="5" t="n"/>
       <c r="L25" s="8" t="n"/>
-      <c r="M25" s="8">
-        <f>IF(L25="","",L25*20)</f>
-        <v/>
-      </c>
-      <c r="N25" s="8" t="n"/>
+      <c r="M25" s="8" t="n"/>
+      <c r="N25" s="8">
+        <f>IF(M25="","",M25*20)</f>
+        <v/>
+      </c>
       <c r="O25" s="8" t="n"/>
-      <c r="P25" s="8">
-        <f>IF(D25="","",SUM(K25,M25,N25,O25))</f>
+      <c r="P25" s="8" t="n"/>
+      <c r="Q25" s="8">
+        <f>IF(D25="","",SUM(L25,N25,O25,P25))</f>
         <v/>
       </c>
     </row>
@@ -1327,24 +1356,25 @@
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="11" t="n"/>
-      <c r="F26" s="12" t="n"/>
+      <c r="F26" s="11" t="n"/>
       <c r="G26" s="12" t="n"/>
-      <c r="H26" s="11" t="n"/>
-      <c r="I26" s="13">
-        <f>IF(F26="","",MAX(0,(G26-F26)*24-H26/60))</f>
-        <v/>
-      </c>
-      <c r="J26" s="11" t="n"/>
-      <c r="K26" s="14" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="11" t="n"/>
+      <c r="J26" s="13">
+        <f>IF(G26="","",MAX(0,(H26-G26)*24-I26/60))</f>
+        <v/>
+      </c>
+      <c r="K26" s="11" t="n"/>
       <c r="L26" s="14" t="n"/>
-      <c r="M26" s="14">
-        <f>IF(L26="","",L26*20)</f>
-        <v/>
-      </c>
-      <c r="N26" s="14" t="n"/>
+      <c r="M26" s="14" t="n"/>
+      <c r="N26" s="14">
+        <f>IF(M26="","",M26*20)</f>
+        <v/>
+      </c>
       <c r="O26" s="14" t="n"/>
-      <c r="P26" s="14">
-        <f>IF(D26="","",SUM(K26,M26,N26,O26))</f>
+      <c r="P26" s="14" t="n"/>
+      <c r="Q26" s="14">
+        <f>IF(D26="","",SUM(L26,N26,O26,P26))</f>
         <v/>
       </c>
     </row>
@@ -1357,24 +1387,25 @@
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
-      <c r="F27" s="6" t="n"/>
+      <c r="F27" s="5" t="n"/>
       <c r="G27" s="6" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="7">
-        <f>IF(F27="","",MAX(0,(G27-F27)*24-H27/60))</f>
-        <v/>
-      </c>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="8" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="7">
+        <f>IF(G27="","",MAX(0,(H27-G27)*24-I27/60))</f>
+        <v/>
+      </c>
+      <c r="K27" s="5" t="n"/>
       <c r="L27" s="8" t="n"/>
-      <c r="M27" s="8">
-        <f>IF(L27="","",L27*20)</f>
-        <v/>
-      </c>
-      <c r="N27" s="8" t="n"/>
+      <c r="M27" s="8" t="n"/>
+      <c r="N27" s="8">
+        <f>IF(M27="","",M27*20)</f>
+        <v/>
+      </c>
       <c r="O27" s="8" t="n"/>
-      <c r="P27" s="8">
-        <f>IF(D27="","",SUM(K27,M27,N27,O27))</f>
+      <c r="P27" s="8" t="n"/>
+      <c r="Q27" s="8">
+        <f>IF(D27="","",SUM(L27,N27,O27,P27))</f>
         <v/>
       </c>
     </row>
@@ -1387,24 +1418,25 @@
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="11" t="n"/>
-      <c r="F28" s="12" t="n"/>
+      <c r="F28" s="11" t="n"/>
       <c r="G28" s="12" t="n"/>
-      <c r="H28" s="11" t="n"/>
-      <c r="I28" s="13">
-        <f>IF(F28="","",MAX(0,(G28-F28)*24-H28/60))</f>
-        <v/>
-      </c>
-      <c r="J28" s="11" t="n"/>
-      <c r="K28" s="14" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="13">
+        <f>IF(G28="","",MAX(0,(H28-G28)*24-I28/60))</f>
+        <v/>
+      </c>
+      <c r="K28" s="11" t="n"/>
       <c r="L28" s="14" t="n"/>
-      <c r="M28" s="14">
-        <f>IF(L28="","",L28*20)</f>
-        <v/>
-      </c>
-      <c r="N28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
+      <c r="N28" s="14">
+        <f>IF(M28="","",M28*20)</f>
+        <v/>
+      </c>
       <c r="O28" s="14" t="n"/>
-      <c r="P28" s="14">
-        <f>IF(D28="","",SUM(K28,M28,N28,O28))</f>
+      <c r="P28" s="14" t="n"/>
+      <c r="Q28" s="14">
+        <f>IF(D28="","",SUM(L28,N28,O28,P28))</f>
         <v/>
       </c>
     </row>
@@ -1417,24 +1449,25 @@
       <c r="C29" s="5" t="n"/>
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="5" t="n"/>
-      <c r="F29" s="6" t="n"/>
+      <c r="F29" s="5" t="n"/>
       <c r="G29" s="6" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="7">
-        <f>IF(F29="","",MAX(0,(G29-F29)*24-H29/60))</f>
-        <v/>
-      </c>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="8" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="7">
+        <f>IF(G29="","",MAX(0,(H29-G29)*24-I29/60))</f>
+        <v/>
+      </c>
+      <c r="K29" s="5" t="n"/>
       <c r="L29" s="8" t="n"/>
-      <c r="M29" s="8">
-        <f>IF(L29="","",L29*20)</f>
-        <v/>
-      </c>
-      <c r="N29" s="8" t="n"/>
+      <c r="M29" s="8" t="n"/>
+      <c r="N29" s="8">
+        <f>IF(M29="","",M29*20)</f>
+        <v/>
+      </c>
       <c r="O29" s="8" t="n"/>
-      <c r="P29" s="8">
-        <f>IF(D29="","",SUM(K29,M29,N29,O29))</f>
+      <c r="P29" s="8" t="n"/>
+      <c r="Q29" s="8">
+        <f>IF(D29="","",SUM(L29,N29,O29,P29))</f>
         <v/>
       </c>
     </row>
@@ -1447,24 +1480,25 @@
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="11" t="n"/>
-      <c r="F30" s="12" t="n"/>
+      <c r="F30" s="11" t="n"/>
       <c r="G30" s="12" t="n"/>
-      <c r="H30" s="11" t="n"/>
-      <c r="I30" s="13">
-        <f>IF(F30="","",MAX(0,(G30-F30)*24-H30/60))</f>
-        <v/>
-      </c>
-      <c r="J30" s="11" t="n"/>
-      <c r="K30" s="14" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="13">
+        <f>IF(G30="","",MAX(0,(H30-G30)*24-I30/60))</f>
+        <v/>
+      </c>
+      <c r="K30" s="11" t="n"/>
       <c r="L30" s="14" t="n"/>
-      <c r="M30" s="14">
-        <f>IF(L30="","",L30*20)</f>
-        <v/>
-      </c>
-      <c r="N30" s="14" t="n"/>
+      <c r="M30" s="14" t="n"/>
+      <c r="N30" s="14">
+        <f>IF(M30="","",M30*20)</f>
+        <v/>
+      </c>
       <c r="O30" s="14" t="n"/>
-      <c r="P30" s="14">
-        <f>IF(D30="","",SUM(K30,M30,N30,O30))</f>
+      <c r="P30" s="14" t="n"/>
+      <c r="Q30" s="14">
+        <f>IF(D30="","",SUM(L30,N30,O30,P30))</f>
         <v/>
       </c>
     </row>
@@ -1477,24 +1511,25 @@
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
-      <c r="F31" s="6" t="n"/>
+      <c r="F31" s="5" t="n"/>
       <c r="G31" s="6" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="7">
-        <f>IF(F31="","",MAX(0,(G31-F31)*24-H31/60))</f>
-        <v/>
-      </c>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="8" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="7">
+        <f>IF(G31="","",MAX(0,(H31-G31)*24-I31/60))</f>
+        <v/>
+      </c>
+      <c r="K31" s="5" t="n"/>
       <c r="L31" s="8" t="n"/>
-      <c r="M31" s="8">
-        <f>IF(L31="","",L31*20)</f>
-        <v/>
-      </c>
-      <c r="N31" s="8" t="n"/>
+      <c r="M31" s="8" t="n"/>
+      <c r="N31" s="8">
+        <f>IF(M31="","",M31*20)</f>
+        <v/>
+      </c>
       <c r="O31" s="8" t="n"/>
-      <c r="P31" s="8">
-        <f>IF(D31="","",SUM(K31,M31,N31,O31))</f>
+      <c r="P31" s="8" t="n"/>
+      <c r="Q31" s="8">
+        <f>IF(D31="","",SUM(L31,N31,O31,P31))</f>
         <v/>
       </c>
     </row>
@@ -1507,24 +1542,25 @@
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="11" t="n"/>
-      <c r="F32" s="12" t="n"/>
+      <c r="F32" s="11" t="n"/>
       <c r="G32" s="12" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="13">
-        <f>IF(F32="","",MAX(0,(G32-F32)*24-H32/60))</f>
-        <v/>
-      </c>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="14" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="11" t="n"/>
+      <c r="J32" s="13">
+        <f>IF(G32="","",MAX(0,(H32-G32)*24-I32/60))</f>
+        <v/>
+      </c>
+      <c r="K32" s="11" t="n"/>
       <c r="L32" s="14" t="n"/>
-      <c r="M32" s="14">
-        <f>IF(L32="","",L32*20)</f>
-        <v/>
-      </c>
-      <c r="N32" s="14" t="n"/>
+      <c r="M32" s="14" t="n"/>
+      <c r="N32" s="14">
+        <f>IF(M32="","",M32*20)</f>
+        <v/>
+      </c>
       <c r="O32" s="14" t="n"/>
-      <c r="P32" s="14">
-        <f>IF(D32="","",SUM(K32,M32,N32,O32))</f>
+      <c r="P32" s="14" t="n"/>
+      <c r="Q32" s="14">
+        <f>IF(D32="","",SUM(L32,N32,O32,P32))</f>
         <v/>
       </c>
     </row>
@@ -1537,24 +1573,25 @@
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
-      <c r="F33" s="6" t="n"/>
+      <c r="F33" s="5" t="n"/>
       <c r="G33" s="6" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="7">
-        <f>IF(F33="","",MAX(0,(G33-F33)*24-H33/60))</f>
-        <v/>
-      </c>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="8" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="7">
+        <f>IF(G33="","",MAX(0,(H33-G33)*24-I33/60))</f>
+        <v/>
+      </c>
+      <c r="K33" s="5" t="n"/>
       <c r="L33" s="8" t="n"/>
-      <c r="M33" s="8">
-        <f>IF(L33="","",L33*20)</f>
-        <v/>
-      </c>
-      <c r="N33" s="8" t="n"/>
+      <c r="M33" s="8" t="n"/>
+      <c r="N33" s="8">
+        <f>IF(M33="","",M33*20)</f>
+        <v/>
+      </c>
       <c r="O33" s="8" t="n"/>
-      <c r="P33" s="8">
-        <f>IF(D33="","",SUM(K33,M33,N33,O33))</f>
+      <c r="P33" s="8" t="n"/>
+      <c r="Q33" s="8">
+        <f>IF(D33="","",SUM(L33,N33,O33,P33))</f>
         <v/>
       </c>
     </row>
@@ -1567,24 +1604,25 @@
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="11" t="n"/>
-      <c r="F34" s="12" t="n"/>
+      <c r="F34" s="11" t="n"/>
       <c r="G34" s="12" t="n"/>
-      <c r="H34" s="11" t="n"/>
-      <c r="I34" s="13">
-        <f>IF(F34="","",MAX(0,(G34-F34)*24-H34/60))</f>
-        <v/>
-      </c>
-      <c r="J34" s="11" t="n"/>
-      <c r="K34" s="14" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="11" t="n"/>
+      <c r="J34" s="13">
+        <f>IF(G34="","",MAX(0,(H34-G34)*24-I34/60))</f>
+        <v/>
+      </c>
+      <c r="K34" s="11" t="n"/>
       <c r="L34" s="14" t="n"/>
-      <c r="M34" s="14">
-        <f>IF(L34="","",L34*20)</f>
-        <v/>
-      </c>
-      <c r="N34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
+      <c r="N34" s="14">
+        <f>IF(M34="","",M34*20)</f>
+        <v/>
+      </c>
       <c r="O34" s="14" t="n"/>
-      <c r="P34" s="14">
-        <f>IF(D34="","",SUM(K34,M34,N34,O34))</f>
+      <c r="P34" s="14" t="n"/>
+      <c r="Q34" s="14">
+        <f>IF(D34="","",SUM(L34,N34,O34,P34))</f>
         <v/>
       </c>
     </row>
@@ -1597,24 +1635,25 @@
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
-      <c r="F35" s="6" t="n"/>
+      <c r="F35" s="5" t="n"/>
       <c r="G35" s="6" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="7">
-        <f>IF(F35="","",MAX(0,(G35-F35)*24-H35/60))</f>
-        <v/>
-      </c>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="8" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="7">
+        <f>IF(G35="","",MAX(0,(H35-G35)*24-I35/60))</f>
+        <v/>
+      </c>
+      <c r="K35" s="5" t="n"/>
       <c r="L35" s="8" t="n"/>
-      <c r="M35" s="8">
-        <f>IF(L35="","",L35*20)</f>
-        <v/>
-      </c>
-      <c r="N35" s="8" t="n"/>
+      <c r="M35" s="8" t="n"/>
+      <c r="N35" s="8">
+        <f>IF(M35="","",M35*20)</f>
+        <v/>
+      </c>
       <c r="O35" s="8" t="n"/>
-      <c r="P35" s="8">
-        <f>IF(D35="","",SUM(K35,M35,N35,O35))</f>
+      <c r="P35" s="8" t="n"/>
+      <c r="Q35" s="8">
+        <f>IF(D35="","",SUM(L35,N35,O35,P35))</f>
         <v/>
       </c>
     </row>
@@ -1627,24 +1666,25 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="11" t="n"/>
-      <c r="F36" s="12" t="n"/>
+      <c r="F36" s="11" t="n"/>
       <c r="G36" s="12" t="n"/>
-      <c r="H36" s="11" t="n"/>
-      <c r="I36" s="13">
-        <f>IF(F36="","",MAX(0,(G36-F36)*24-H36/60))</f>
-        <v/>
-      </c>
-      <c r="J36" s="11" t="n"/>
-      <c r="K36" s="14" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="11" t="n"/>
+      <c r="J36" s="13">
+        <f>IF(G36="","",MAX(0,(H36-G36)*24-I36/60))</f>
+        <v/>
+      </c>
+      <c r="K36" s="11" t="n"/>
       <c r="L36" s="14" t="n"/>
-      <c r="M36" s="14">
-        <f>IF(L36="","",L36*20)</f>
-        <v/>
-      </c>
-      <c r="N36" s="14" t="n"/>
+      <c r="M36" s="14" t="n"/>
+      <c r="N36" s="14">
+        <f>IF(M36="","",M36*20)</f>
+        <v/>
+      </c>
       <c r="O36" s="14" t="n"/>
-      <c r="P36" s="14">
-        <f>IF(D36="","",SUM(K36,M36,N36,O36))</f>
+      <c r="P36" s="14" t="n"/>
+      <c r="Q36" s="14">
+        <f>IF(D36="","",SUM(L36,N36,O36,P36))</f>
         <v/>
       </c>
     </row>
@@ -1657,24 +1697,25 @@
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="5" t="n"/>
       <c r="E37" s="5" t="n"/>
-      <c r="F37" s="6" t="n"/>
+      <c r="F37" s="5" t="n"/>
       <c r="G37" s="6" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="7">
-        <f>IF(F37="","",MAX(0,(G37-F37)*24-H37/60))</f>
-        <v/>
-      </c>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="8" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="7">
+        <f>IF(G37="","",MAX(0,(H37-G37)*24-I37/60))</f>
+        <v/>
+      </c>
+      <c r="K37" s="5" t="n"/>
       <c r="L37" s="8" t="n"/>
-      <c r="M37" s="8">
-        <f>IF(L37="","",L37*20)</f>
-        <v/>
-      </c>
-      <c r="N37" s="8" t="n"/>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="8">
+        <f>IF(M37="","",M37*20)</f>
+        <v/>
+      </c>
       <c r="O37" s="8" t="n"/>
-      <c r="P37" s="8">
-        <f>IF(D37="","",SUM(K37,M37,N37,O37))</f>
+      <c r="P37" s="8" t="n"/>
+      <c r="Q37" s="8">
+        <f>IF(D37="","",SUM(L37,N37,O37,P37))</f>
         <v/>
       </c>
     </row>
@@ -1687,24 +1728,25 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="11" t="n"/>
-      <c r="F38" s="12" t="n"/>
+      <c r="F38" s="11" t="n"/>
       <c r="G38" s="12" t="n"/>
-      <c r="H38" s="11" t="n"/>
-      <c r="I38" s="13">
-        <f>IF(F38="","",MAX(0,(G38-F38)*24-H38/60))</f>
-        <v/>
-      </c>
-      <c r="J38" s="11" t="n"/>
-      <c r="K38" s="14" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="11" t="n"/>
+      <c r="J38" s="13">
+        <f>IF(G38="","",MAX(0,(H38-G38)*24-I38/60))</f>
+        <v/>
+      </c>
+      <c r="K38" s="11" t="n"/>
       <c r="L38" s="14" t="n"/>
-      <c r="M38" s="14">
-        <f>IF(L38="","",L38*20)</f>
-        <v/>
-      </c>
-      <c r="N38" s="14" t="n"/>
+      <c r="M38" s="14" t="n"/>
+      <c r="N38" s="14">
+        <f>IF(M38="","",M38*20)</f>
+        <v/>
+      </c>
       <c r="O38" s="14" t="n"/>
-      <c r="P38" s="14">
-        <f>IF(D38="","",SUM(K38,M38,N38,O38))</f>
+      <c r="P38" s="14" t="n"/>
+      <c r="Q38" s="14">
+        <f>IF(D38="","",SUM(L38,N38,O38,P38))</f>
         <v/>
       </c>
     </row>
@@ -1717,24 +1759,25 @@
       <c r="C39" s="5" t="n"/>
       <c r="D39" s="5" t="n"/>
       <c r="E39" s="5" t="n"/>
-      <c r="F39" s="6" t="n"/>
+      <c r="F39" s="5" t="n"/>
       <c r="G39" s="6" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="7">
-        <f>IF(F39="","",MAX(0,(G39-F39)*24-H39/60))</f>
-        <v/>
-      </c>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="8" t="n"/>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="7">
+        <f>IF(G39="","",MAX(0,(H39-G39)*24-I39/60))</f>
+        <v/>
+      </c>
+      <c r="K39" s="5" t="n"/>
       <c r="L39" s="8" t="n"/>
-      <c r="M39" s="8">
-        <f>IF(L39="","",L39*20)</f>
-        <v/>
-      </c>
-      <c r="N39" s="8" t="n"/>
+      <c r="M39" s="8" t="n"/>
+      <c r="N39" s="8">
+        <f>IF(M39="","",M39*20)</f>
+        <v/>
+      </c>
       <c r="O39" s="8" t="n"/>
-      <c r="P39" s="8">
-        <f>IF(D39="","",SUM(K39,M39,N39,O39))</f>
+      <c r="P39" s="8" t="n"/>
+      <c r="Q39" s="8">
+        <f>IF(D39="","",SUM(L39,N39,O39,P39))</f>
         <v/>
       </c>
     </row>
@@ -1747,24 +1790,25 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="11" t="n"/>
-      <c r="F40" s="12" t="n"/>
+      <c r="F40" s="11" t="n"/>
       <c r="G40" s="12" t="n"/>
-      <c r="H40" s="11" t="n"/>
-      <c r="I40" s="13">
-        <f>IF(F40="","",MAX(0,(G40-F40)*24-H40/60))</f>
-        <v/>
-      </c>
-      <c r="J40" s="11" t="n"/>
-      <c r="K40" s="14" t="n"/>
+      <c r="H40" s="12" t="n"/>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="13">
+        <f>IF(G40="","",MAX(0,(H40-G40)*24-I40/60))</f>
+        <v/>
+      </c>
+      <c r="K40" s="11" t="n"/>
       <c r="L40" s="14" t="n"/>
-      <c r="M40" s="14">
-        <f>IF(L40="","",L40*20)</f>
-        <v/>
-      </c>
-      <c r="N40" s="14" t="n"/>
+      <c r="M40" s="14" t="n"/>
+      <c r="N40" s="14">
+        <f>IF(M40="","",M40*20)</f>
+        <v/>
+      </c>
       <c r="O40" s="14" t="n"/>
-      <c r="P40" s="14">
-        <f>IF(D40="","",SUM(K40,M40,N40,O40))</f>
+      <c r="P40" s="14" t="n"/>
+      <c r="Q40" s="14">
+        <f>IF(D40="","",SUM(L40,N40,O40,P40))</f>
         <v/>
       </c>
     </row>
@@ -1777,24 +1821,25 @@
       <c r="C41" s="5" t="n"/>
       <c r="D41" s="5" t="n"/>
       <c r="E41" s="5" t="n"/>
-      <c r="F41" s="6" t="n"/>
+      <c r="F41" s="5" t="n"/>
       <c r="G41" s="6" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="7">
-        <f>IF(F41="","",MAX(0,(G41-F41)*24-H41/60))</f>
-        <v/>
-      </c>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="8" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="7">
+        <f>IF(G41="","",MAX(0,(H41-G41)*24-I41/60))</f>
+        <v/>
+      </c>
+      <c r="K41" s="5" t="n"/>
       <c r="L41" s="8" t="n"/>
-      <c r="M41" s="8">
-        <f>IF(L41="","",L41*20)</f>
-        <v/>
-      </c>
-      <c r="N41" s="8" t="n"/>
+      <c r="M41" s="8" t="n"/>
+      <c r="N41" s="8">
+        <f>IF(M41="","",M41*20)</f>
+        <v/>
+      </c>
       <c r="O41" s="8" t="n"/>
-      <c r="P41" s="8">
-        <f>IF(D41="","",SUM(K41,M41,N41,O41))</f>
+      <c r="P41" s="8" t="n"/>
+      <c r="Q41" s="8">
+        <f>IF(D41="","",SUM(L41,N41,O41,P41))</f>
         <v/>
       </c>
     </row>
@@ -1807,24 +1852,25 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="11" t="n"/>
-      <c r="F42" s="12" t="n"/>
+      <c r="F42" s="11" t="n"/>
       <c r="G42" s="12" t="n"/>
-      <c r="H42" s="11" t="n"/>
-      <c r="I42" s="13">
-        <f>IF(F42="","",MAX(0,(G42-F42)*24-H42/60))</f>
-        <v/>
-      </c>
-      <c r="J42" s="11" t="n"/>
-      <c r="K42" s="14" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="13">
+        <f>IF(G42="","",MAX(0,(H42-G42)*24-I42/60))</f>
+        <v/>
+      </c>
+      <c r="K42" s="11" t="n"/>
       <c r="L42" s="14" t="n"/>
-      <c r="M42" s="14">
-        <f>IF(L42="","",L42*20)</f>
-        <v/>
-      </c>
-      <c r="N42" s="14" t="n"/>
+      <c r="M42" s="14" t="n"/>
+      <c r="N42" s="14">
+        <f>IF(M42="","",M42*20)</f>
+        <v/>
+      </c>
       <c r="O42" s="14" t="n"/>
-      <c r="P42" s="14">
-        <f>IF(D42="","",SUM(K42,M42,N42,O42))</f>
+      <c r="P42" s="14" t="n"/>
+      <c r="Q42" s="14">
+        <f>IF(D42="","",SUM(L42,N42,O42,P42))</f>
         <v/>
       </c>
     </row>
@@ -1837,24 +1883,25 @@
       <c r="C43" s="5" t="n"/>
       <c r="D43" s="5" t="n"/>
       <c r="E43" s="5" t="n"/>
-      <c r="F43" s="6" t="n"/>
+      <c r="F43" s="5" t="n"/>
       <c r="G43" s="6" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="7">
-        <f>IF(F43="","",MAX(0,(G43-F43)*24-H43/60))</f>
-        <v/>
-      </c>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="8" t="n"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="7">
+        <f>IF(G43="","",MAX(0,(H43-G43)*24-I43/60))</f>
+        <v/>
+      </c>
+      <c r="K43" s="5" t="n"/>
       <c r="L43" s="8" t="n"/>
-      <c r="M43" s="8">
-        <f>IF(L43="","",L43*20)</f>
-        <v/>
-      </c>
-      <c r="N43" s="8" t="n"/>
+      <c r="M43" s="8" t="n"/>
+      <c r="N43" s="8">
+        <f>IF(M43="","",M43*20)</f>
+        <v/>
+      </c>
       <c r="O43" s="8" t="n"/>
-      <c r="P43" s="8">
-        <f>IF(D43="","",SUM(K43,M43,N43,O43))</f>
+      <c r="P43" s="8" t="n"/>
+      <c r="Q43" s="8">
+        <f>IF(D43="","",SUM(L43,N43,O43,P43))</f>
         <v/>
       </c>
     </row>
@@ -1867,24 +1914,25 @@
       <c r="C44" s="11" t="n"/>
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="11" t="n"/>
-      <c r="F44" s="12" t="n"/>
+      <c r="F44" s="11" t="n"/>
       <c r="G44" s="12" t="n"/>
-      <c r="H44" s="11" t="n"/>
-      <c r="I44" s="13">
-        <f>IF(F44="","",MAX(0,(G44-F44)*24-H44/60))</f>
-        <v/>
-      </c>
-      <c r="J44" s="11" t="n"/>
-      <c r="K44" s="14" t="n"/>
+      <c r="H44" s="12" t="n"/>
+      <c r="I44" s="11" t="n"/>
+      <c r="J44" s="13">
+        <f>IF(G44="","",MAX(0,(H44-G44)*24-I44/60))</f>
+        <v/>
+      </c>
+      <c r="K44" s="11" t="n"/>
       <c r="L44" s="14" t="n"/>
-      <c r="M44" s="14">
-        <f>IF(L44="","",L44*20)</f>
-        <v/>
-      </c>
-      <c r="N44" s="14" t="n"/>
+      <c r="M44" s="14" t="n"/>
+      <c r="N44" s="14">
+        <f>IF(M44="","",M44*20)</f>
+        <v/>
+      </c>
       <c r="O44" s="14" t="n"/>
-      <c r="P44" s="14">
-        <f>IF(D44="","",SUM(K44,M44,N44,O44))</f>
+      <c r="P44" s="14" t="n"/>
+      <c r="Q44" s="14">
+        <f>IF(D44="","",SUM(L44,N44,O44,P44))</f>
         <v/>
       </c>
     </row>
@@ -1897,24 +1945,25 @@
       <c r="C45" s="5" t="n"/>
       <c r="D45" s="5" t="n"/>
       <c r="E45" s="5" t="n"/>
-      <c r="F45" s="6" t="n"/>
+      <c r="F45" s="5" t="n"/>
       <c r="G45" s="6" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="7">
-        <f>IF(F45="","",MAX(0,(G45-F45)*24-H45/60))</f>
-        <v/>
-      </c>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="8" t="n"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="7">
+        <f>IF(G45="","",MAX(0,(H45-G45)*24-I45/60))</f>
+        <v/>
+      </c>
+      <c r="K45" s="5" t="n"/>
       <c r="L45" s="8" t="n"/>
-      <c r="M45" s="8">
-        <f>IF(L45="","",L45*20)</f>
-        <v/>
-      </c>
-      <c r="N45" s="8" t="n"/>
+      <c r="M45" s="8" t="n"/>
+      <c r="N45" s="8">
+        <f>IF(M45="","",M45*20)</f>
+        <v/>
+      </c>
       <c r="O45" s="8" t="n"/>
-      <c r="P45" s="8">
-        <f>IF(D45="","",SUM(K45,M45,N45,O45))</f>
+      <c r="P45" s="8" t="n"/>
+      <c r="Q45" s="8">
+        <f>IF(D45="","",SUM(L45,N45,O45,P45))</f>
         <v/>
       </c>
     </row>
@@ -1927,24 +1976,25 @@
       <c r="C46" s="11" t="n"/>
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="11" t="n"/>
-      <c r="F46" s="12" t="n"/>
+      <c r="F46" s="11" t="n"/>
       <c r="G46" s="12" t="n"/>
-      <c r="H46" s="11" t="n"/>
-      <c r="I46" s="13">
-        <f>IF(F46="","",MAX(0,(G46-F46)*24-H46/60))</f>
-        <v/>
-      </c>
-      <c r="J46" s="11" t="n"/>
-      <c r="K46" s="14" t="n"/>
+      <c r="H46" s="12" t="n"/>
+      <c r="I46" s="11" t="n"/>
+      <c r="J46" s="13">
+        <f>IF(G46="","",MAX(0,(H46-G46)*24-I46/60))</f>
+        <v/>
+      </c>
+      <c r="K46" s="11" t="n"/>
       <c r="L46" s="14" t="n"/>
-      <c r="M46" s="14">
-        <f>IF(L46="","",L46*20)</f>
-        <v/>
-      </c>
-      <c r="N46" s="14" t="n"/>
+      <c r="M46" s="14" t="n"/>
+      <c r="N46" s="14">
+        <f>IF(M46="","",M46*20)</f>
+        <v/>
+      </c>
       <c r="O46" s="14" t="n"/>
-      <c r="P46" s="14">
-        <f>IF(D46="","",SUM(K46,M46,N46,O46))</f>
+      <c r="P46" s="14" t="n"/>
+      <c r="Q46" s="14">
+        <f>IF(D46="","",SUM(L46,N46,O46,P46))</f>
         <v/>
       </c>
     </row>
@@ -1957,24 +2007,25 @@
       <c r="C47" s="5" t="n"/>
       <c r="D47" s="5" t="n"/>
       <c r="E47" s="5" t="n"/>
-      <c r="F47" s="6" t="n"/>
+      <c r="F47" s="5" t="n"/>
       <c r="G47" s="6" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="7">
-        <f>IF(F47="","",MAX(0,(G47-F47)*24-H47/60))</f>
-        <v/>
-      </c>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="8" t="n"/>
+      <c r="H47" s="6" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="7">
+        <f>IF(G47="","",MAX(0,(H47-G47)*24-I47/60))</f>
+        <v/>
+      </c>
+      <c r="K47" s="5" t="n"/>
       <c r="L47" s="8" t="n"/>
-      <c r="M47" s="8">
-        <f>IF(L47="","",L47*20)</f>
-        <v/>
-      </c>
-      <c r="N47" s="8" t="n"/>
+      <c r="M47" s="8" t="n"/>
+      <c r="N47" s="8">
+        <f>IF(M47="","",M47*20)</f>
+        <v/>
+      </c>
       <c r="O47" s="8" t="n"/>
-      <c r="P47" s="8">
-        <f>IF(D47="","",SUM(K47,M47,N47,O47))</f>
+      <c r="P47" s="8" t="n"/>
+      <c r="Q47" s="8">
+        <f>IF(D47="","",SUM(L47,N47,O47,P47))</f>
         <v/>
       </c>
     </row>
@@ -1987,24 +2038,25 @@
       <c r="C48" s="11" t="n"/>
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="11" t="n"/>
-      <c r="F48" s="12" t="n"/>
+      <c r="F48" s="11" t="n"/>
       <c r="G48" s="12" t="n"/>
-      <c r="H48" s="11" t="n"/>
-      <c r="I48" s="13">
-        <f>IF(F48="","",MAX(0,(G48-F48)*24-H48/60))</f>
-        <v/>
-      </c>
-      <c r="J48" s="11" t="n"/>
-      <c r="K48" s="14" t="n"/>
+      <c r="H48" s="12" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="13">
+        <f>IF(G48="","",MAX(0,(H48-G48)*24-I48/60))</f>
+        <v/>
+      </c>
+      <c r="K48" s="11" t="n"/>
       <c r="L48" s="14" t="n"/>
-      <c r="M48" s="14">
-        <f>IF(L48="","",L48*20)</f>
-        <v/>
-      </c>
-      <c r="N48" s="14" t="n"/>
+      <c r="M48" s="14" t="n"/>
+      <c r="N48" s="14">
+        <f>IF(M48="","",M48*20)</f>
+        <v/>
+      </c>
       <c r="O48" s="14" t="n"/>
-      <c r="P48" s="14">
-        <f>IF(D48="","",SUM(K48,M48,N48,O48))</f>
+      <c r="P48" s="14" t="n"/>
+      <c r="Q48" s="14">
+        <f>IF(D48="","",SUM(L48,N48,O48,P48))</f>
         <v/>
       </c>
     </row>
@@ -2017,24 +2069,25 @@
       <c r="C49" s="5" t="n"/>
       <c r="D49" s="5" t="n"/>
       <c r="E49" s="5" t="n"/>
-      <c r="F49" s="6" t="n"/>
+      <c r="F49" s="5" t="n"/>
       <c r="G49" s="6" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="7">
-        <f>IF(F49="","",MAX(0,(G49-F49)*24-H49/60))</f>
-        <v/>
-      </c>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="8" t="n"/>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="7">
+        <f>IF(G49="","",MAX(0,(H49-G49)*24-I49/60))</f>
+        <v/>
+      </c>
+      <c r="K49" s="5" t="n"/>
       <c r="L49" s="8" t="n"/>
-      <c r="M49" s="8">
-        <f>IF(L49="","",L49*20)</f>
-        <v/>
-      </c>
-      <c r="N49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8">
+        <f>IF(M49="","",M49*20)</f>
+        <v/>
+      </c>
       <c r="O49" s="8" t="n"/>
-      <c r="P49" s="8">
-        <f>IF(D49="","",SUM(K49,M49,N49,O49))</f>
+      <c r="P49" s="8" t="n"/>
+      <c r="Q49" s="8">
+        <f>IF(D49="","",SUM(L49,N49,O49,P49))</f>
         <v/>
       </c>
     </row>
@@ -2047,24 +2100,25 @@
       <c r="C50" s="11" t="n"/>
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="11" t="n"/>
-      <c r="F50" s="12" t="n"/>
+      <c r="F50" s="11" t="n"/>
       <c r="G50" s="12" t="n"/>
-      <c r="H50" s="11" t="n"/>
-      <c r="I50" s="13">
-        <f>IF(F50="","",MAX(0,(G50-F50)*24-H50/60))</f>
-        <v/>
-      </c>
-      <c r="J50" s="11" t="n"/>
-      <c r="K50" s="14" t="n"/>
+      <c r="H50" s="12" t="n"/>
+      <c r="I50" s="11" t="n"/>
+      <c r="J50" s="13">
+        <f>IF(G50="","",MAX(0,(H50-G50)*24-I50/60))</f>
+        <v/>
+      </c>
+      <c r="K50" s="11" t="n"/>
       <c r="L50" s="14" t="n"/>
-      <c r="M50" s="14">
-        <f>IF(L50="","",L50*20)</f>
-        <v/>
-      </c>
-      <c r="N50" s="14" t="n"/>
+      <c r="M50" s="14" t="n"/>
+      <c r="N50" s="14">
+        <f>IF(M50="","",M50*20)</f>
+        <v/>
+      </c>
       <c r="O50" s="14" t="n"/>
-      <c r="P50" s="14">
-        <f>IF(D50="","",SUM(K50,M50,N50,O50))</f>
+      <c r="P50" s="14" t="n"/>
+      <c r="Q50" s="14">
+        <f>IF(D50="","",SUM(L50,N50,O50,P50))</f>
         <v/>
       </c>
     </row>
@@ -2077,24 +2131,25 @@
       <c r="C51" s="5" t="n"/>
       <c r="D51" s="5" t="n"/>
       <c r="E51" s="5" t="n"/>
-      <c r="F51" s="6" t="n"/>
+      <c r="F51" s="5" t="n"/>
       <c r="G51" s="6" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="7">
-        <f>IF(F51="","",MAX(0,(G51-F51)*24-H51/60))</f>
-        <v/>
-      </c>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="8" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="7">
+        <f>IF(G51="","",MAX(0,(H51-G51)*24-I51/60))</f>
+        <v/>
+      </c>
+      <c r="K51" s="5" t="n"/>
       <c r="L51" s="8" t="n"/>
-      <c r="M51" s="8">
-        <f>IF(L51="","",L51*20)</f>
-        <v/>
-      </c>
-      <c r="N51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
+      <c r="N51" s="8">
+        <f>IF(M51="","",M51*20)</f>
+        <v/>
+      </c>
       <c r="O51" s="8" t="n"/>
-      <c r="P51" s="8">
-        <f>IF(D51="","",SUM(K51,M51,N51,O51))</f>
+      <c r="P51" s="8" t="n"/>
+      <c r="Q51" s="8">
+        <f>IF(D51="","",SUM(L51,N51,O51,P51))</f>
         <v/>
       </c>
     </row>
@@ -2107,24 +2162,25 @@
       <c r="C52" s="11" t="n"/>
       <c r="D52" s="11" t="n"/>
       <c r="E52" s="11" t="n"/>
-      <c r="F52" s="12" t="n"/>
+      <c r="F52" s="11" t="n"/>
       <c r="G52" s="12" t="n"/>
-      <c r="H52" s="11" t="n"/>
-      <c r="I52" s="13">
-        <f>IF(F52="","",MAX(0,(G52-F52)*24-H52/60))</f>
-        <v/>
-      </c>
-      <c r="J52" s="11" t="n"/>
-      <c r="K52" s="14" t="n"/>
+      <c r="H52" s="12" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="13">
+        <f>IF(G52="","",MAX(0,(H52-G52)*24-I52/60))</f>
+        <v/>
+      </c>
+      <c r="K52" s="11" t="n"/>
       <c r="L52" s="14" t="n"/>
-      <c r="M52" s="14">
-        <f>IF(L52="","",L52*20)</f>
-        <v/>
-      </c>
-      <c r="N52" s="14" t="n"/>
+      <c r="M52" s="14" t="n"/>
+      <c r="N52" s="14">
+        <f>IF(M52="","",M52*20)</f>
+        <v/>
+      </c>
       <c r="O52" s="14" t="n"/>
-      <c r="P52" s="14">
-        <f>IF(D52="","",SUM(K52,M52,N52,O52))</f>
+      <c r="P52" s="14" t="n"/>
+      <c r="Q52" s="14">
+        <f>IF(D52="","",SUM(L52,N52,O52,P52))</f>
         <v/>
       </c>
     </row>
@@ -2137,24 +2193,25 @@
       <c r="C53" s="5" t="n"/>
       <c r="D53" s="5" t="n"/>
       <c r="E53" s="5" t="n"/>
-      <c r="F53" s="6" t="n"/>
+      <c r="F53" s="5" t="n"/>
       <c r="G53" s="6" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="7">
-        <f>IF(F53="","",MAX(0,(G53-F53)*24-H53/60))</f>
-        <v/>
-      </c>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="8" t="n"/>
+      <c r="H53" s="6" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="7">
+        <f>IF(G53="","",MAX(0,(H53-G53)*24-I53/60))</f>
+        <v/>
+      </c>
+      <c r="K53" s="5" t="n"/>
       <c r="L53" s="8" t="n"/>
-      <c r="M53" s="8">
-        <f>IF(L53="","",L53*20)</f>
-        <v/>
-      </c>
-      <c r="N53" s="8" t="n"/>
+      <c r="M53" s="8" t="n"/>
+      <c r="N53" s="8">
+        <f>IF(M53="","",M53*20)</f>
+        <v/>
+      </c>
       <c r="O53" s="8" t="n"/>
-      <c r="P53" s="8">
-        <f>IF(D53="","",SUM(K53,M53,N53,O53))</f>
+      <c r="P53" s="8" t="n"/>
+      <c r="Q53" s="8">
+        <f>IF(D53="","",SUM(L53,N53,O53,P53))</f>
         <v/>
       </c>
     </row>
@@ -2167,24 +2224,25 @@
       <c r="C54" s="11" t="n"/>
       <c r="D54" s="11" t="n"/>
       <c r="E54" s="11" t="n"/>
-      <c r="F54" s="12" t="n"/>
+      <c r="F54" s="11" t="n"/>
       <c r="G54" s="12" t="n"/>
-      <c r="H54" s="11" t="n"/>
-      <c r="I54" s="13">
-        <f>IF(F54="","",MAX(0,(G54-F54)*24-H54/60))</f>
-        <v/>
-      </c>
-      <c r="J54" s="11" t="n"/>
-      <c r="K54" s="14" t="n"/>
+      <c r="H54" s="12" t="n"/>
+      <c r="I54" s="11" t="n"/>
+      <c r="J54" s="13">
+        <f>IF(G54="","",MAX(0,(H54-G54)*24-I54/60))</f>
+        <v/>
+      </c>
+      <c r="K54" s="11" t="n"/>
       <c r="L54" s="14" t="n"/>
-      <c r="M54" s="14">
-        <f>IF(L54="","",L54*20)</f>
-        <v/>
-      </c>
-      <c r="N54" s="14" t="n"/>
+      <c r="M54" s="14" t="n"/>
+      <c r="N54" s="14">
+        <f>IF(M54="","",M54*20)</f>
+        <v/>
+      </c>
       <c r="O54" s="14" t="n"/>
-      <c r="P54" s="14">
-        <f>IF(D54="","",SUM(K54,M54,N54,O54))</f>
+      <c r="P54" s="14" t="n"/>
+      <c r="Q54" s="14">
+        <f>IF(D54="","",SUM(L54,N54,O54,P54))</f>
         <v/>
       </c>
     </row>
@@ -2197,24 +2255,25 @@
       <c r="C55" s="5" t="n"/>
       <c r="D55" s="5" t="n"/>
       <c r="E55" s="5" t="n"/>
-      <c r="F55" s="6" t="n"/>
+      <c r="F55" s="5" t="n"/>
       <c r="G55" s="6" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="7">
-        <f>IF(F55="","",MAX(0,(G55-F55)*24-H55/60))</f>
-        <v/>
-      </c>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="8" t="n"/>
+      <c r="H55" s="6" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="7">
+        <f>IF(G55="","",MAX(0,(H55-G55)*24-I55/60))</f>
+        <v/>
+      </c>
+      <c r="K55" s="5" t="n"/>
       <c r="L55" s="8" t="n"/>
-      <c r="M55" s="8">
-        <f>IF(L55="","",L55*20)</f>
-        <v/>
-      </c>
-      <c r="N55" s="8" t="n"/>
+      <c r="M55" s="8" t="n"/>
+      <c r="N55" s="8">
+        <f>IF(M55="","",M55*20)</f>
+        <v/>
+      </c>
       <c r="O55" s="8" t="n"/>
-      <c r="P55" s="8">
-        <f>IF(D55="","",SUM(K55,M55,N55,O55))</f>
+      <c r="P55" s="8" t="n"/>
+      <c r="Q55" s="8">
+        <f>IF(D55="","",SUM(L55,N55,O55,P55))</f>
         <v/>
       </c>
     </row>
@@ -2227,24 +2286,25 @@
       <c r="C56" s="11" t="n"/>
       <c r="D56" s="11" t="n"/>
       <c r="E56" s="11" t="n"/>
-      <c r="F56" s="12" t="n"/>
+      <c r="F56" s="11" t="n"/>
       <c r="G56" s="12" t="n"/>
-      <c r="H56" s="11" t="n"/>
-      <c r="I56" s="13">
-        <f>IF(F56="","",MAX(0,(G56-F56)*24-H56/60))</f>
-        <v/>
-      </c>
-      <c r="J56" s="11" t="n"/>
-      <c r="K56" s="14" t="n"/>
+      <c r="H56" s="12" t="n"/>
+      <c r="I56" s="11" t="n"/>
+      <c r="J56" s="13">
+        <f>IF(G56="","",MAX(0,(H56-G56)*24-I56/60))</f>
+        <v/>
+      </c>
+      <c r="K56" s="11" t="n"/>
       <c r="L56" s="14" t="n"/>
-      <c r="M56" s="14">
-        <f>IF(L56="","",L56*20)</f>
-        <v/>
-      </c>
-      <c r="N56" s="14" t="n"/>
+      <c r="M56" s="14" t="n"/>
+      <c r="N56" s="14">
+        <f>IF(M56="","",M56*20)</f>
+        <v/>
+      </c>
       <c r="O56" s="14" t="n"/>
-      <c r="P56" s="14">
-        <f>IF(D56="","",SUM(K56,M56,N56,O56))</f>
+      <c r="P56" s="14" t="n"/>
+      <c r="Q56" s="14">
+        <f>IF(D56="","",SUM(L56,N56,O56,P56))</f>
         <v/>
       </c>
     </row>
@@ -2257,24 +2317,25 @@
       <c r="C57" s="5" t="n"/>
       <c r="D57" s="5" t="n"/>
       <c r="E57" s="5" t="n"/>
-      <c r="F57" s="6" t="n"/>
+      <c r="F57" s="5" t="n"/>
       <c r="G57" s="6" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="7">
-        <f>IF(F57="","",MAX(0,(G57-F57)*24-H57/60))</f>
-        <v/>
-      </c>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="8" t="n"/>
+      <c r="H57" s="6" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="7">
+        <f>IF(G57="","",MAX(0,(H57-G57)*24-I57/60))</f>
+        <v/>
+      </c>
+      <c r="K57" s="5" t="n"/>
       <c r="L57" s="8" t="n"/>
-      <c r="M57" s="8">
-        <f>IF(L57="","",L57*20)</f>
-        <v/>
-      </c>
-      <c r="N57" s="8" t="n"/>
+      <c r="M57" s="8" t="n"/>
+      <c r="N57" s="8">
+        <f>IF(M57="","",M57*20)</f>
+        <v/>
+      </c>
       <c r="O57" s="8" t="n"/>
-      <c r="P57" s="8">
-        <f>IF(D57="","",SUM(K57,M57,N57,O57))</f>
+      <c r="P57" s="8" t="n"/>
+      <c r="Q57" s="8">
+        <f>IF(D57="","",SUM(L57,N57,O57,P57))</f>
         <v/>
       </c>
     </row>
@@ -2287,24 +2348,25 @@
       <c r="C58" s="11" t="n"/>
       <c r="D58" s="11" t="n"/>
       <c r="E58" s="11" t="n"/>
-      <c r="F58" s="12" t="n"/>
+      <c r="F58" s="11" t="n"/>
       <c r="G58" s="12" t="n"/>
-      <c r="H58" s="11" t="n"/>
-      <c r="I58" s="13">
-        <f>IF(F58="","",MAX(0,(G58-F58)*24-H58/60))</f>
-        <v/>
-      </c>
-      <c r="J58" s="11" t="n"/>
-      <c r="K58" s="14" t="n"/>
+      <c r="H58" s="12" t="n"/>
+      <c r="I58" s="11" t="n"/>
+      <c r="J58" s="13">
+        <f>IF(G58="","",MAX(0,(H58-G58)*24-I58/60))</f>
+        <v/>
+      </c>
+      <c r="K58" s="11" t="n"/>
       <c r="L58" s="14" t="n"/>
-      <c r="M58" s="14">
-        <f>IF(L58="","",L58*20)</f>
-        <v/>
-      </c>
-      <c r="N58" s="14" t="n"/>
+      <c r="M58" s="14" t="n"/>
+      <c r="N58" s="14">
+        <f>IF(M58="","",M58*20)</f>
+        <v/>
+      </c>
       <c r="O58" s="14" t="n"/>
-      <c r="P58" s="14">
-        <f>IF(D58="","",SUM(K58,M58,N58,O58))</f>
+      <c r="P58" s="14" t="n"/>
+      <c r="Q58" s="14">
+        <f>IF(D58="","",SUM(L58,N58,O58,P58))</f>
         <v/>
       </c>
     </row>
@@ -2317,24 +2379,25 @@
       <c r="C59" s="5" t="n"/>
       <c r="D59" s="5" t="n"/>
       <c r="E59" s="5" t="n"/>
-      <c r="F59" s="6" t="n"/>
+      <c r="F59" s="5" t="n"/>
       <c r="G59" s="6" t="n"/>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="7">
-        <f>IF(F59="","",MAX(0,(G59-F59)*24-H59/60))</f>
-        <v/>
-      </c>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="8" t="n"/>
+      <c r="H59" s="6" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="7">
+        <f>IF(G59="","",MAX(0,(H59-G59)*24-I59/60))</f>
+        <v/>
+      </c>
+      <c r="K59" s="5" t="n"/>
       <c r="L59" s="8" t="n"/>
-      <c r="M59" s="8">
-        <f>IF(L59="","",L59*20)</f>
-        <v/>
-      </c>
-      <c r="N59" s="8" t="n"/>
+      <c r="M59" s="8" t="n"/>
+      <c r="N59" s="8">
+        <f>IF(M59="","",M59*20)</f>
+        <v/>
+      </c>
       <c r="O59" s="8" t="n"/>
-      <c r="P59" s="8">
-        <f>IF(D59="","",SUM(K59,M59,N59,O59))</f>
+      <c r="P59" s="8" t="n"/>
+      <c r="Q59" s="8">
+        <f>IF(D59="","",SUM(L59,N59,O59,P59))</f>
         <v/>
       </c>
     </row>
@@ -2347,24 +2410,25 @@
       <c r="C60" s="11" t="n"/>
       <c r="D60" s="11" t="n"/>
       <c r="E60" s="11" t="n"/>
-      <c r="F60" s="12" t="n"/>
+      <c r="F60" s="11" t="n"/>
       <c r="G60" s="12" t="n"/>
-      <c r="H60" s="11" t="n"/>
-      <c r="I60" s="13">
-        <f>IF(F60="","",MAX(0,(G60-F60)*24-H60/60))</f>
-        <v/>
-      </c>
-      <c r="J60" s="11" t="n"/>
-      <c r="K60" s="14" t="n"/>
+      <c r="H60" s="12" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="13">
+        <f>IF(G60="","",MAX(0,(H60-G60)*24-I60/60))</f>
+        <v/>
+      </c>
+      <c r="K60" s="11" t="n"/>
       <c r="L60" s="14" t="n"/>
-      <c r="M60" s="14">
-        <f>IF(L60="","",L60*20)</f>
-        <v/>
-      </c>
-      <c r="N60" s="14" t="n"/>
+      <c r="M60" s="14" t="n"/>
+      <c r="N60" s="14">
+        <f>IF(M60="","",M60*20)</f>
+        <v/>
+      </c>
       <c r="O60" s="14" t="n"/>
-      <c r="P60" s="14">
-        <f>IF(D60="","",SUM(K60,M60,N60,O60))</f>
+      <c r="P60" s="14" t="n"/>
+      <c r="Q60" s="14">
+        <f>IF(D60="","",SUM(L60,N60,O60,P60))</f>
         <v/>
       </c>
     </row>
@@ -2377,24 +2441,25 @@
       <c r="C61" s="5" t="n"/>
       <c r="D61" s="5" t="n"/>
       <c r="E61" s="5" t="n"/>
-      <c r="F61" s="6" t="n"/>
+      <c r="F61" s="5" t="n"/>
       <c r="G61" s="6" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="7">
-        <f>IF(F61="","",MAX(0,(G61-F61)*24-H61/60))</f>
-        <v/>
-      </c>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="8" t="n"/>
+      <c r="H61" s="6" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="7">
+        <f>IF(G61="","",MAX(0,(H61-G61)*24-I61/60))</f>
+        <v/>
+      </c>
+      <c r="K61" s="5" t="n"/>
       <c r="L61" s="8" t="n"/>
-      <c r="M61" s="8">
-        <f>IF(L61="","",L61*20)</f>
-        <v/>
-      </c>
-      <c r="N61" s="8" t="n"/>
+      <c r="M61" s="8" t="n"/>
+      <c r="N61" s="8">
+        <f>IF(M61="","",M61*20)</f>
+        <v/>
+      </c>
       <c r="O61" s="8" t="n"/>
-      <c r="P61" s="8">
-        <f>IF(D61="","",SUM(K61,M61,N61,O61))</f>
+      <c r="P61" s="8" t="n"/>
+      <c r="Q61" s="8">
+        <f>IF(D61="","",SUM(L61,N61,O61,P61))</f>
         <v/>
       </c>
     </row>
@@ -2407,24 +2472,25 @@
       <c r="C62" s="11" t="n"/>
       <c r="D62" s="11" t="n"/>
       <c r="E62" s="11" t="n"/>
-      <c r="F62" s="12" t="n"/>
+      <c r="F62" s="11" t="n"/>
       <c r="G62" s="12" t="n"/>
-      <c r="H62" s="11" t="n"/>
-      <c r="I62" s="13">
-        <f>IF(F62="","",MAX(0,(G62-F62)*24-H62/60))</f>
-        <v/>
-      </c>
-      <c r="J62" s="11" t="n"/>
-      <c r="K62" s="14" t="n"/>
+      <c r="H62" s="12" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="13">
+        <f>IF(G62="","",MAX(0,(H62-G62)*24-I62/60))</f>
+        <v/>
+      </c>
+      <c r="K62" s="11" t="n"/>
       <c r="L62" s="14" t="n"/>
-      <c r="M62" s="14">
-        <f>IF(L62="","",L62*20)</f>
-        <v/>
-      </c>
-      <c r="N62" s="14" t="n"/>
+      <c r="M62" s="14" t="n"/>
+      <c r="N62" s="14">
+        <f>IF(M62="","",M62*20)</f>
+        <v/>
+      </c>
       <c r="O62" s="14" t="n"/>
-      <c r="P62" s="14">
-        <f>IF(D62="","",SUM(K62,M62,N62,O62))</f>
+      <c r="P62" s="14" t="n"/>
+      <c r="Q62" s="14">
+        <f>IF(D62="","",SUM(L62,N62,O62,P62))</f>
         <v/>
       </c>
     </row>
@@ -2437,24 +2503,25 @@
       <c r="C63" s="5" t="n"/>
       <c r="D63" s="5" t="n"/>
       <c r="E63" s="5" t="n"/>
-      <c r="F63" s="6" t="n"/>
+      <c r="F63" s="5" t="n"/>
       <c r="G63" s="6" t="n"/>
-      <c r="H63" s="5" t="n"/>
-      <c r="I63" s="7">
-        <f>IF(F63="","",MAX(0,(G63-F63)*24-H63/60))</f>
-        <v/>
-      </c>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="8" t="n"/>
+      <c r="H63" s="6" t="n"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="7">
+        <f>IF(G63="","",MAX(0,(H63-G63)*24-I63/60))</f>
+        <v/>
+      </c>
+      <c r="K63" s="5" t="n"/>
       <c r="L63" s="8" t="n"/>
-      <c r="M63" s="8">
-        <f>IF(L63="","",L63*20)</f>
-        <v/>
-      </c>
-      <c r="N63" s="8" t="n"/>
+      <c r="M63" s="8" t="n"/>
+      <c r="N63" s="8">
+        <f>IF(M63="","",M63*20)</f>
+        <v/>
+      </c>
       <c r="O63" s="8" t="n"/>
-      <c r="P63" s="8">
-        <f>IF(D63="","",SUM(K63,M63,N63,O63))</f>
+      <c r="P63" s="8" t="n"/>
+      <c r="Q63" s="8">
+        <f>IF(D63="","",SUM(L63,N63,O63,P63))</f>
         <v/>
       </c>
     </row>
@@ -2467,24 +2534,25 @@
       <c r="C64" s="11" t="n"/>
       <c r="D64" s="11" t="n"/>
       <c r="E64" s="11" t="n"/>
-      <c r="F64" s="12" t="n"/>
+      <c r="F64" s="11" t="n"/>
       <c r="G64" s="12" t="n"/>
-      <c r="H64" s="11" t="n"/>
-      <c r="I64" s="13">
-        <f>IF(F64="","",MAX(0,(G64-F64)*24-H64/60))</f>
-        <v/>
-      </c>
-      <c r="J64" s="11" t="n"/>
-      <c r="K64" s="14" t="n"/>
+      <c r="H64" s="12" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="13">
+        <f>IF(G64="","",MAX(0,(H64-G64)*24-I64/60))</f>
+        <v/>
+      </c>
+      <c r="K64" s="11" t="n"/>
       <c r="L64" s="14" t="n"/>
-      <c r="M64" s="14">
-        <f>IF(L64="","",L64*20)</f>
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n"/>
+      <c r="M64" s="14" t="n"/>
+      <c r="N64" s="14">
+        <f>IF(M64="","",M64*20)</f>
+        <v/>
+      </c>
       <c r="O64" s="14" t="n"/>
-      <c r="P64" s="14">
-        <f>IF(D64="","",SUM(K64,M64,N64,O64))</f>
+      <c r="P64" s="14" t="n"/>
+      <c r="Q64" s="14">
+        <f>IF(D64="","",SUM(L64,N64,O64,P64))</f>
         <v/>
       </c>
     </row>
@@ -2497,24 +2565,25 @@
       <c r="C65" s="5" t="n"/>
       <c r="D65" s="5" t="n"/>
       <c r="E65" s="5" t="n"/>
-      <c r="F65" s="6" t="n"/>
+      <c r="F65" s="5" t="n"/>
       <c r="G65" s="6" t="n"/>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="7">
-        <f>IF(F65="","",MAX(0,(G65-F65)*24-H65/60))</f>
-        <v/>
-      </c>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="8" t="n"/>
+      <c r="H65" s="6" t="n"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="7">
+        <f>IF(G65="","",MAX(0,(H65-G65)*24-I65/60))</f>
+        <v/>
+      </c>
+      <c r="K65" s="5" t="n"/>
       <c r="L65" s="8" t="n"/>
-      <c r="M65" s="8">
-        <f>IF(L65="","",L65*20)</f>
-        <v/>
-      </c>
-      <c r="N65" s="8" t="n"/>
+      <c r="M65" s="8" t="n"/>
+      <c r="N65" s="8">
+        <f>IF(M65="","",M65*20)</f>
+        <v/>
+      </c>
       <c r="O65" s="8" t="n"/>
-      <c r="P65" s="8">
-        <f>IF(D65="","",SUM(K65,M65,N65,O65))</f>
+      <c r="P65" s="8" t="n"/>
+      <c r="Q65" s="8">
+        <f>IF(D65="","",SUM(L65,N65,O65,P65))</f>
         <v/>
       </c>
     </row>
@@ -2527,24 +2596,25 @@
       <c r="C66" s="11" t="n"/>
       <c r="D66" s="11" t="n"/>
       <c r="E66" s="11" t="n"/>
-      <c r="F66" s="12" t="n"/>
+      <c r="F66" s="11" t="n"/>
       <c r="G66" s="12" t="n"/>
-      <c r="H66" s="11" t="n"/>
-      <c r="I66" s="13">
-        <f>IF(F66="","",MAX(0,(G66-F66)*24-H66/60))</f>
-        <v/>
-      </c>
-      <c r="J66" s="11" t="n"/>
-      <c r="K66" s="14" t="n"/>
+      <c r="H66" s="12" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="13">
+        <f>IF(G66="","",MAX(0,(H66-G66)*24-I66/60))</f>
+        <v/>
+      </c>
+      <c r="K66" s="11" t="n"/>
       <c r="L66" s="14" t="n"/>
-      <c r="M66" s="14">
-        <f>IF(L66="","",L66*20)</f>
-        <v/>
-      </c>
-      <c r="N66" s="14" t="n"/>
+      <c r="M66" s="14" t="n"/>
+      <c r="N66" s="14">
+        <f>IF(M66="","",M66*20)</f>
+        <v/>
+      </c>
       <c r="O66" s="14" t="n"/>
-      <c r="P66" s="14">
-        <f>IF(D66="","",SUM(K66,M66,N66,O66))</f>
+      <c r="P66" s="14" t="n"/>
+      <c r="Q66" s="14">
+        <f>IF(D66="","",SUM(L66,N66,O66,P66))</f>
         <v/>
       </c>
     </row>
@@ -2557,24 +2627,25 @@
       <c r="C67" s="5" t="n"/>
       <c r="D67" s="5" t="n"/>
       <c r="E67" s="5" t="n"/>
-      <c r="F67" s="6" t="n"/>
+      <c r="F67" s="5" t="n"/>
       <c r="G67" s="6" t="n"/>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="7">
-        <f>IF(F67="","",MAX(0,(G67-F67)*24-H67/60))</f>
-        <v/>
-      </c>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="8" t="n"/>
+      <c r="H67" s="6" t="n"/>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="7">
+        <f>IF(G67="","",MAX(0,(H67-G67)*24-I67/60))</f>
+        <v/>
+      </c>
+      <c r="K67" s="5" t="n"/>
       <c r="L67" s="8" t="n"/>
-      <c r="M67" s="8">
-        <f>IF(L67="","",L67*20)</f>
-        <v/>
-      </c>
-      <c r="N67" s="8" t="n"/>
+      <c r="M67" s="8" t="n"/>
+      <c r="N67" s="8">
+        <f>IF(M67="","",M67*20)</f>
+        <v/>
+      </c>
       <c r="O67" s="8" t="n"/>
-      <c r="P67" s="8">
-        <f>IF(D67="","",SUM(K67,M67,N67,O67))</f>
+      <c r="P67" s="8" t="n"/>
+      <c r="Q67" s="8">
+        <f>IF(D67="","",SUM(L67,N67,O67,P67))</f>
         <v/>
       </c>
     </row>
@@ -2587,24 +2658,25 @@
       <c r="C68" s="11" t="n"/>
       <c r="D68" s="11" t="n"/>
       <c r="E68" s="11" t="n"/>
-      <c r="F68" s="12" t="n"/>
+      <c r="F68" s="11" t="n"/>
       <c r="G68" s="12" t="n"/>
-      <c r="H68" s="11" t="n"/>
-      <c r="I68" s="13">
-        <f>IF(F68="","",MAX(0,(G68-F68)*24-H68/60))</f>
-        <v/>
-      </c>
-      <c r="J68" s="11" t="n"/>
-      <c r="K68" s="14" t="n"/>
+      <c r="H68" s="12" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="13">
+        <f>IF(G68="","",MAX(0,(H68-G68)*24-I68/60))</f>
+        <v/>
+      </c>
+      <c r="K68" s="11" t="n"/>
       <c r="L68" s="14" t="n"/>
-      <c r="M68" s="14">
-        <f>IF(L68="","",L68*20)</f>
-        <v/>
-      </c>
-      <c r="N68" s="14" t="n"/>
+      <c r="M68" s="14" t="n"/>
+      <c r="N68" s="14">
+        <f>IF(M68="","",M68*20)</f>
+        <v/>
+      </c>
       <c r="O68" s="14" t="n"/>
-      <c r="P68" s="14">
-        <f>IF(D68="","",SUM(K68,M68,N68,O68))</f>
+      <c r="P68" s="14" t="n"/>
+      <c r="Q68" s="14">
+        <f>IF(D68="","",SUM(L68,N68,O68,P68))</f>
         <v/>
       </c>
     </row>
@@ -2617,24 +2689,25 @@
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="5" t="n"/>
       <c r="E69" s="5" t="n"/>
-      <c r="F69" s="6" t="n"/>
+      <c r="F69" s="5" t="n"/>
       <c r="G69" s="6" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="7">
-        <f>IF(F69="","",MAX(0,(G69-F69)*24-H69/60))</f>
-        <v/>
-      </c>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="8" t="n"/>
+      <c r="H69" s="6" t="n"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="7">
+        <f>IF(G69="","",MAX(0,(H69-G69)*24-I69/60))</f>
+        <v/>
+      </c>
+      <c r="K69" s="5" t="n"/>
       <c r="L69" s="8" t="n"/>
-      <c r="M69" s="8">
-        <f>IF(L69="","",L69*20)</f>
-        <v/>
-      </c>
-      <c r="N69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
+      <c r="N69" s="8">
+        <f>IF(M69="","",M69*20)</f>
+        <v/>
+      </c>
       <c r="O69" s="8" t="n"/>
-      <c r="P69" s="8">
-        <f>IF(D69="","",SUM(K69,M69,N69,O69))</f>
+      <c r="P69" s="8" t="n"/>
+      <c r="Q69" s="8">
+        <f>IF(D69="","",SUM(L69,N69,O69,P69))</f>
         <v/>
       </c>
     </row>
@@ -2647,24 +2720,25 @@
       <c r="C70" s="11" t="n"/>
       <c r="D70" s="11" t="n"/>
       <c r="E70" s="11" t="n"/>
-      <c r="F70" s="12" t="n"/>
+      <c r="F70" s="11" t="n"/>
       <c r="G70" s="12" t="n"/>
-      <c r="H70" s="11" t="n"/>
-      <c r="I70" s="13">
-        <f>IF(F70="","",MAX(0,(G70-F70)*24-H70/60))</f>
-        <v/>
-      </c>
-      <c r="J70" s="11" t="n"/>
-      <c r="K70" s="14" t="n"/>
+      <c r="H70" s="12" t="n"/>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="13">
+        <f>IF(G70="","",MAX(0,(H70-G70)*24-I70/60))</f>
+        <v/>
+      </c>
+      <c r="K70" s="11" t="n"/>
       <c r="L70" s="14" t="n"/>
-      <c r="M70" s="14">
-        <f>IF(L70="","",L70*20)</f>
-        <v/>
-      </c>
-      <c r="N70" s="14" t="n"/>
+      <c r="M70" s="14" t="n"/>
+      <c r="N70" s="14">
+        <f>IF(M70="","",M70*20)</f>
+        <v/>
+      </c>
       <c r="O70" s="14" t="n"/>
-      <c r="P70" s="14">
-        <f>IF(D70="","",SUM(K70,M70,N70,O70))</f>
+      <c r="P70" s="14" t="n"/>
+      <c r="Q70" s="14">
+        <f>IF(D70="","",SUM(L70,N70,O70,P70))</f>
         <v/>
       </c>
     </row>
@@ -2677,24 +2751,25 @@
       <c r="C71" s="5" t="n"/>
       <c r="D71" s="5" t="n"/>
       <c r="E71" s="5" t="n"/>
-      <c r="F71" s="6" t="n"/>
+      <c r="F71" s="5" t="n"/>
       <c r="G71" s="6" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="7">
-        <f>IF(F71="","",MAX(0,(G71-F71)*24-H71/60))</f>
-        <v/>
-      </c>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="8" t="n"/>
+      <c r="H71" s="6" t="n"/>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="7">
+        <f>IF(G71="","",MAX(0,(H71-G71)*24-I71/60))</f>
+        <v/>
+      </c>
+      <c r="K71" s="5" t="n"/>
       <c r="L71" s="8" t="n"/>
-      <c r="M71" s="8">
-        <f>IF(L71="","",L71*20)</f>
-        <v/>
-      </c>
-      <c r="N71" s="8" t="n"/>
+      <c r="M71" s="8" t="n"/>
+      <c r="N71" s="8">
+        <f>IF(M71="","",M71*20)</f>
+        <v/>
+      </c>
       <c r="O71" s="8" t="n"/>
-      <c r="P71" s="8">
-        <f>IF(D71="","",SUM(K71,M71,N71,O71))</f>
+      <c r="P71" s="8" t="n"/>
+      <c r="Q71" s="8">
+        <f>IF(D71="","",SUM(L71,N71,O71,P71))</f>
         <v/>
       </c>
     </row>
@@ -2707,24 +2782,25 @@
       <c r="C72" s="11" t="n"/>
       <c r="D72" s="11" t="n"/>
       <c r="E72" s="11" t="n"/>
-      <c r="F72" s="12" t="n"/>
+      <c r="F72" s="11" t="n"/>
       <c r="G72" s="12" t="n"/>
-      <c r="H72" s="11" t="n"/>
-      <c r="I72" s="13">
-        <f>IF(F72="","",MAX(0,(G72-F72)*24-H72/60))</f>
-        <v/>
-      </c>
-      <c r="J72" s="11" t="n"/>
-      <c r="K72" s="14" t="n"/>
+      <c r="H72" s="12" t="n"/>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="13">
+        <f>IF(G72="","",MAX(0,(H72-G72)*24-I72/60))</f>
+        <v/>
+      </c>
+      <c r="K72" s="11" t="n"/>
       <c r="L72" s="14" t="n"/>
-      <c r="M72" s="14">
-        <f>IF(L72="","",L72*20)</f>
-        <v/>
-      </c>
-      <c r="N72" s="14" t="n"/>
+      <c r="M72" s="14" t="n"/>
+      <c r="N72" s="14">
+        <f>IF(M72="","",M72*20)</f>
+        <v/>
+      </c>
       <c r="O72" s="14" t="n"/>
-      <c r="P72" s="14">
-        <f>IF(D72="","",SUM(K72,M72,N72,O72))</f>
+      <c r="P72" s="14" t="n"/>
+      <c r="Q72" s="14">
+        <f>IF(D72="","",SUM(L72,N72,O72,P72))</f>
         <v/>
       </c>
     </row>
@@ -2737,24 +2813,25 @@
       <c r="C73" s="5" t="n"/>
       <c r="D73" s="5" t="n"/>
       <c r="E73" s="5" t="n"/>
-      <c r="F73" s="6" t="n"/>
+      <c r="F73" s="5" t="n"/>
       <c r="G73" s="6" t="n"/>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="7">
-        <f>IF(F73="","",MAX(0,(G73-F73)*24-H73/60))</f>
-        <v/>
-      </c>
-      <c r="J73" s="5" t="n"/>
-      <c r="K73" s="8" t="n"/>
+      <c r="H73" s="6" t="n"/>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="7">
+        <f>IF(G73="","",MAX(0,(H73-G73)*24-I73/60))</f>
+        <v/>
+      </c>
+      <c r="K73" s="5" t="n"/>
       <c r="L73" s="8" t="n"/>
-      <c r="M73" s="8">
-        <f>IF(L73="","",L73*20)</f>
-        <v/>
-      </c>
-      <c r="N73" s="8" t="n"/>
+      <c r="M73" s="8" t="n"/>
+      <c r="N73" s="8">
+        <f>IF(M73="","",M73*20)</f>
+        <v/>
+      </c>
       <c r="O73" s="8" t="n"/>
-      <c r="P73" s="8">
-        <f>IF(D73="","",SUM(K73,M73,N73,O73))</f>
+      <c r="P73" s="8" t="n"/>
+      <c r="Q73" s="8">
+        <f>IF(D73="","",SUM(L73,N73,O73,P73))</f>
         <v/>
       </c>
     </row>
@@ -2767,24 +2844,25 @@
       <c r="C74" s="11" t="n"/>
       <c r="D74" s="11" t="n"/>
       <c r="E74" s="11" t="n"/>
-      <c r="F74" s="12" t="n"/>
+      <c r="F74" s="11" t="n"/>
       <c r="G74" s="12" t="n"/>
-      <c r="H74" s="11" t="n"/>
-      <c r="I74" s="13">
-        <f>IF(F74="","",MAX(0,(G74-F74)*24-H74/60))</f>
-        <v/>
-      </c>
-      <c r="J74" s="11" t="n"/>
-      <c r="K74" s="14" t="n"/>
+      <c r="H74" s="12" t="n"/>
+      <c r="I74" s="11" t="n"/>
+      <c r="J74" s="13">
+        <f>IF(G74="","",MAX(0,(H74-G74)*24-I74/60))</f>
+        <v/>
+      </c>
+      <c r="K74" s="11" t="n"/>
       <c r="L74" s="14" t="n"/>
-      <c r="M74" s="14">
-        <f>IF(L74="","",L74*20)</f>
-        <v/>
-      </c>
-      <c r="N74" s="14" t="n"/>
+      <c r="M74" s="14" t="n"/>
+      <c r="N74" s="14">
+        <f>IF(M74="","",M74*20)</f>
+        <v/>
+      </c>
       <c r="O74" s="14" t="n"/>
-      <c r="P74" s="14">
-        <f>IF(D74="","",SUM(K74,M74,N74,O74))</f>
+      <c r="P74" s="14" t="n"/>
+      <c r="Q74" s="14">
+        <f>IF(D74="","",SUM(L74,N74,O74,P74))</f>
         <v/>
       </c>
     </row>
@@ -2797,24 +2875,25 @@
       <c r="C75" s="5" t="n"/>
       <c r="D75" s="5" t="n"/>
       <c r="E75" s="5" t="n"/>
-      <c r="F75" s="6" t="n"/>
+      <c r="F75" s="5" t="n"/>
       <c r="G75" s="6" t="n"/>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="7">
-        <f>IF(F75="","",MAX(0,(G75-F75)*24-H75/60))</f>
-        <v/>
-      </c>
-      <c r="J75" s="5" t="n"/>
-      <c r="K75" s="8" t="n"/>
+      <c r="H75" s="6" t="n"/>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="7">
+        <f>IF(G75="","",MAX(0,(H75-G75)*24-I75/60))</f>
+        <v/>
+      </c>
+      <c r="K75" s="5" t="n"/>
       <c r="L75" s="8" t="n"/>
-      <c r="M75" s="8">
-        <f>IF(L75="","",L75*20)</f>
-        <v/>
-      </c>
-      <c r="N75" s="8" t="n"/>
+      <c r="M75" s="8" t="n"/>
+      <c r="N75" s="8">
+        <f>IF(M75="","",M75*20)</f>
+        <v/>
+      </c>
       <c r="O75" s="8" t="n"/>
-      <c r="P75" s="8">
-        <f>IF(D75="","",SUM(K75,M75,N75,O75))</f>
+      <c r="P75" s="8" t="n"/>
+      <c r="Q75" s="8">
+        <f>IF(D75="","",SUM(L75,N75,O75,P75))</f>
         <v/>
       </c>
     </row>
@@ -2827,24 +2906,25 @@
       <c r="C76" s="11" t="n"/>
       <c r="D76" s="11" t="n"/>
       <c r="E76" s="11" t="n"/>
-      <c r="F76" s="12" t="n"/>
+      <c r="F76" s="11" t="n"/>
       <c r="G76" s="12" t="n"/>
-      <c r="H76" s="11" t="n"/>
-      <c r="I76" s="13">
-        <f>IF(F76="","",MAX(0,(G76-F76)*24-H76/60))</f>
-        <v/>
-      </c>
-      <c r="J76" s="11" t="n"/>
-      <c r="K76" s="14" t="n"/>
+      <c r="H76" s="12" t="n"/>
+      <c r="I76" s="11" t="n"/>
+      <c r="J76" s="13">
+        <f>IF(G76="","",MAX(0,(H76-G76)*24-I76/60))</f>
+        <v/>
+      </c>
+      <c r="K76" s="11" t="n"/>
       <c r="L76" s="14" t="n"/>
-      <c r="M76" s="14">
-        <f>IF(L76="","",L76*20)</f>
-        <v/>
-      </c>
-      <c r="N76" s="14" t="n"/>
+      <c r="M76" s="14" t="n"/>
+      <c r="N76" s="14">
+        <f>IF(M76="","",M76*20)</f>
+        <v/>
+      </c>
       <c r="O76" s="14" t="n"/>
-      <c r="P76" s="14">
-        <f>IF(D76="","",SUM(K76,M76,N76,O76))</f>
+      <c r="P76" s="14" t="n"/>
+      <c r="Q76" s="14">
+        <f>IF(D76="","",SUM(L76,N76,O76,P76))</f>
         <v/>
       </c>
     </row>
@@ -2857,24 +2937,25 @@
       <c r="C77" s="5" t="n"/>
       <c r="D77" s="5" t="n"/>
       <c r="E77" s="5" t="n"/>
-      <c r="F77" s="6" t="n"/>
+      <c r="F77" s="5" t="n"/>
       <c r="G77" s="6" t="n"/>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="7">
-        <f>IF(F77="","",MAX(0,(G77-F77)*24-H77/60))</f>
-        <v/>
-      </c>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="8" t="n"/>
+      <c r="H77" s="6" t="n"/>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="7">
+        <f>IF(G77="","",MAX(0,(H77-G77)*24-I77/60))</f>
+        <v/>
+      </c>
+      <c r="K77" s="5" t="n"/>
       <c r="L77" s="8" t="n"/>
-      <c r="M77" s="8">
-        <f>IF(L77="","",L77*20)</f>
-        <v/>
-      </c>
-      <c r="N77" s="8" t="n"/>
+      <c r="M77" s="8" t="n"/>
+      <c r="N77" s="8">
+        <f>IF(M77="","",M77*20)</f>
+        <v/>
+      </c>
       <c r="O77" s="8" t="n"/>
-      <c r="P77" s="8">
-        <f>IF(D77="","",SUM(K77,M77,N77,O77))</f>
+      <c r="P77" s="8" t="n"/>
+      <c r="Q77" s="8">
+        <f>IF(D77="","",SUM(L77,N77,O77,P77))</f>
         <v/>
       </c>
     </row>
@@ -2887,24 +2968,25 @@
       <c r="C78" s="11" t="n"/>
       <c r="D78" s="11" t="n"/>
       <c r="E78" s="11" t="n"/>
-      <c r="F78" s="12" t="n"/>
+      <c r="F78" s="11" t="n"/>
       <c r="G78" s="12" t="n"/>
-      <c r="H78" s="11" t="n"/>
-      <c r="I78" s="13">
-        <f>IF(F78="","",MAX(0,(G78-F78)*24-H78/60))</f>
-        <v/>
-      </c>
-      <c r="J78" s="11" t="n"/>
-      <c r="K78" s="14" t="n"/>
+      <c r="H78" s="12" t="n"/>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="13">
+        <f>IF(G78="","",MAX(0,(H78-G78)*24-I78/60))</f>
+        <v/>
+      </c>
+      <c r="K78" s="11" t="n"/>
       <c r="L78" s="14" t="n"/>
-      <c r="M78" s="14">
-        <f>IF(L78="","",L78*20)</f>
-        <v/>
-      </c>
-      <c r="N78" s="14" t="n"/>
+      <c r="M78" s="14" t="n"/>
+      <c r="N78" s="14">
+        <f>IF(M78="","",M78*20)</f>
+        <v/>
+      </c>
       <c r="O78" s="14" t="n"/>
-      <c r="P78" s="14">
-        <f>IF(D78="","",SUM(K78,M78,N78,O78))</f>
+      <c r="P78" s="14" t="n"/>
+      <c r="Q78" s="14">
+        <f>IF(D78="","",SUM(L78,N78,O78,P78))</f>
         <v/>
       </c>
     </row>
@@ -2917,24 +2999,25 @@
       <c r="C79" s="5" t="n"/>
       <c r="D79" s="5" t="n"/>
       <c r="E79" s="5" t="n"/>
-      <c r="F79" s="6" t="n"/>
+      <c r="F79" s="5" t="n"/>
       <c r="G79" s="6" t="n"/>
-      <c r="H79" s="5" t="n"/>
-      <c r="I79" s="7">
-        <f>IF(F79="","",MAX(0,(G79-F79)*24-H79/60))</f>
-        <v/>
-      </c>
-      <c r="J79" s="5" t="n"/>
-      <c r="K79" s="8" t="n"/>
+      <c r="H79" s="6" t="n"/>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="7">
+        <f>IF(G79="","",MAX(0,(H79-G79)*24-I79/60))</f>
+        <v/>
+      </c>
+      <c r="K79" s="5" t="n"/>
       <c r="L79" s="8" t="n"/>
-      <c r="M79" s="8">
-        <f>IF(L79="","",L79*20)</f>
-        <v/>
-      </c>
-      <c r="N79" s="8" t="n"/>
+      <c r="M79" s="8" t="n"/>
+      <c r="N79" s="8">
+        <f>IF(M79="","",M79*20)</f>
+        <v/>
+      </c>
       <c r="O79" s="8" t="n"/>
-      <c r="P79" s="8">
-        <f>IF(D79="","",SUM(K79,M79,N79,O79))</f>
+      <c r="P79" s="8" t="n"/>
+      <c r="Q79" s="8">
+        <f>IF(D79="","",SUM(L79,N79,O79,P79))</f>
         <v/>
       </c>
     </row>
@@ -2947,24 +3030,25 @@
       <c r="C80" s="11" t="n"/>
       <c r="D80" s="11" t="n"/>
       <c r="E80" s="11" t="n"/>
-      <c r="F80" s="12" t="n"/>
+      <c r="F80" s="11" t="n"/>
       <c r="G80" s="12" t="n"/>
-      <c r="H80" s="11" t="n"/>
-      <c r="I80" s="13">
-        <f>IF(F80="","",MAX(0,(G80-F80)*24-H80/60))</f>
-        <v/>
-      </c>
-      <c r="J80" s="11" t="n"/>
-      <c r="K80" s="14" t="n"/>
+      <c r="H80" s="12" t="n"/>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="13">
+        <f>IF(G80="","",MAX(0,(H80-G80)*24-I80/60))</f>
+        <v/>
+      </c>
+      <c r="K80" s="11" t="n"/>
       <c r="L80" s="14" t="n"/>
-      <c r="M80" s="14">
-        <f>IF(L80="","",L80*20)</f>
-        <v/>
-      </c>
-      <c r="N80" s="14" t="n"/>
+      <c r="M80" s="14" t="n"/>
+      <c r="N80" s="14">
+        <f>IF(M80="","",M80*20)</f>
+        <v/>
+      </c>
       <c r="O80" s="14" t="n"/>
-      <c r="P80" s="14">
-        <f>IF(D80="","",SUM(K80,M80,N80,O80))</f>
+      <c r="P80" s="14" t="n"/>
+      <c r="Q80" s="14">
+        <f>IF(D80="","",SUM(L80,N80,O80,P80))</f>
         <v/>
       </c>
     </row>
@@ -2977,24 +3061,25 @@
       <c r="C81" s="5" t="n"/>
       <c r="D81" s="5" t="n"/>
       <c r="E81" s="5" t="n"/>
-      <c r="F81" s="6" t="n"/>
+      <c r="F81" s="5" t="n"/>
       <c r="G81" s="6" t="n"/>
-      <c r="H81" s="5" t="n"/>
-      <c r="I81" s="7">
-        <f>IF(F81="","",MAX(0,(G81-F81)*24-H81/60))</f>
-        <v/>
-      </c>
-      <c r="J81" s="5" t="n"/>
-      <c r="K81" s="8" t="n"/>
+      <c r="H81" s="6" t="n"/>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="7">
+        <f>IF(G81="","",MAX(0,(H81-G81)*24-I81/60))</f>
+        <v/>
+      </c>
+      <c r="K81" s="5" t="n"/>
       <c r="L81" s="8" t="n"/>
-      <c r="M81" s="8">
-        <f>IF(L81="","",L81*20)</f>
-        <v/>
-      </c>
-      <c r="N81" s="8" t="n"/>
+      <c r="M81" s="8" t="n"/>
+      <c r="N81" s="8">
+        <f>IF(M81="","",M81*20)</f>
+        <v/>
+      </c>
       <c r="O81" s="8" t="n"/>
-      <c r="P81" s="8">
-        <f>IF(D81="","",SUM(K81,M81,N81,O81))</f>
+      <c r="P81" s="8" t="n"/>
+      <c r="Q81" s="8">
+        <f>IF(D81="","",SUM(L81,N81,O81,P81))</f>
         <v/>
       </c>
     </row>
@@ -3007,24 +3092,25 @@
       <c r="C82" s="11" t="n"/>
       <c r="D82" s="11" t="n"/>
       <c r="E82" s="11" t="n"/>
-      <c r="F82" s="12" t="n"/>
+      <c r="F82" s="11" t="n"/>
       <c r="G82" s="12" t="n"/>
-      <c r="H82" s="11" t="n"/>
-      <c r="I82" s="13">
-        <f>IF(F82="","",MAX(0,(G82-F82)*24-H82/60))</f>
-        <v/>
-      </c>
-      <c r="J82" s="11" t="n"/>
-      <c r="K82" s="14" t="n"/>
+      <c r="H82" s="12" t="n"/>
+      <c r="I82" s="11" t="n"/>
+      <c r="J82" s="13">
+        <f>IF(G82="","",MAX(0,(H82-G82)*24-I82/60))</f>
+        <v/>
+      </c>
+      <c r="K82" s="11" t="n"/>
       <c r="L82" s="14" t="n"/>
-      <c r="M82" s="14">
-        <f>IF(L82="","",L82*20)</f>
-        <v/>
-      </c>
-      <c r="N82" s="14" t="n"/>
+      <c r="M82" s="14" t="n"/>
+      <c r="N82" s="14">
+        <f>IF(M82="","",M82*20)</f>
+        <v/>
+      </c>
       <c r="O82" s="14" t="n"/>
-      <c r="P82" s="14">
-        <f>IF(D82="","",SUM(K82,M82,N82,O82))</f>
+      <c r="P82" s="14" t="n"/>
+      <c r="Q82" s="14">
+        <f>IF(D82="","",SUM(L82,N82,O82,P82))</f>
         <v/>
       </c>
     </row>
@@ -3037,24 +3123,25 @@
       <c r="C83" s="5" t="n"/>
       <c r="D83" s="5" t="n"/>
       <c r="E83" s="5" t="n"/>
-      <c r="F83" s="6" t="n"/>
+      <c r="F83" s="5" t="n"/>
       <c r="G83" s="6" t="n"/>
-      <c r="H83" s="5" t="n"/>
-      <c r="I83" s="7">
-        <f>IF(F83="","",MAX(0,(G83-F83)*24-H83/60))</f>
-        <v/>
-      </c>
-      <c r="J83" s="5" t="n"/>
-      <c r="K83" s="8" t="n"/>
+      <c r="H83" s="6" t="n"/>
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="7">
+        <f>IF(G83="","",MAX(0,(H83-G83)*24-I83/60))</f>
+        <v/>
+      </c>
+      <c r="K83" s="5" t="n"/>
       <c r="L83" s="8" t="n"/>
-      <c r="M83" s="8">
-        <f>IF(L83="","",L83*20)</f>
-        <v/>
-      </c>
-      <c r="N83" s="8" t="n"/>
+      <c r="M83" s="8" t="n"/>
+      <c r="N83" s="8">
+        <f>IF(M83="","",M83*20)</f>
+        <v/>
+      </c>
       <c r="O83" s="8" t="n"/>
-      <c r="P83" s="8">
-        <f>IF(D83="","",SUM(K83,M83,N83,O83))</f>
+      <c r="P83" s="8" t="n"/>
+      <c r="Q83" s="8">
+        <f>IF(D83="","",SUM(L83,N83,O83,P83))</f>
         <v/>
       </c>
     </row>
@@ -3067,24 +3154,25 @@
       <c r="C84" s="11" t="n"/>
       <c r="D84" s="11" t="n"/>
       <c r="E84" s="11" t="n"/>
-      <c r="F84" s="12" t="n"/>
+      <c r="F84" s="11" t="n"/>
       <c r="G84" s="12" t="n"/>
-      <c r="H84" s="11" t="n"/>
-      <c r="I84" s="13">
-        <f>IF(F84="","",MAX(0,(G84-F84)*24-H84/60))</f>
-        <v/>
-      </c>
-      <c r="J84" s="11" t="n"/>
-      <c r="K84" s="14" t="n"/>
+      <c r="H84" s="12" t="n"/>
+      <c r="I84" s="11" t="n"/>
+      <c r="J84" s="13">
+        <f>IF(G84="","",MAX(0,(H84-G84)*24-I84/60))</f>
+        <v/>
+      </c>
+      <c r="K84" s="11" t="n"/>
       <c r="L84" s="14" t="n"/>
-      <c r="M84" s="14">
-        <f>IF(L84="","",L84*20)</f>
-        <v/>
-      </c>
-      <c r="N84" s="14" t="n"/>
+      <c r="M84" s="14" t="n"/>
+      <c r="N84" s="14">
+        <f>IF(M84="","",M84*20)</f>
+        <v/>
+      </c>
       <c r="O84" s="14" t="n"/>
-      <c r="P84" s="14">
-        <f>IF(D84="","",SUM(K84,M84,N84,O84))</f>
+      <c r="P84" s="14" t="n"/>
+      <c r="Q84" s="14">
+        <f>IF(D84="","",SUM(L84,N84,O84,P84))</f>
         <v/>
       </c>
     </row>
@@ -3097,24 +3185,25 @@
       <c r="C85" s="5" t="n"/>
       <c r="D85" s="5" t="n"/>
       <c r="E85" s="5" t="n"/>
-      <c r="F85" s="6" t="n"/>
+      <c r="F85" s="5" t="n"/>
       <c r="G85" s="6" t="n"/>
-      <c r="H85" s="5" t="n"/>
-      <c r="I85" s="7">
-        <f>IF(F85="","",MAX(0,(G85-F85)*24-H85/60))</f>
-        <v/>
-      </c>
-      <c r="J85" s="5" t="n"/>
-      <c r="K85" s="8" t="n"/>
+      <c r="H85" s="6" t="n"/>
+      <c r="I85" s="5" t="n"/>
+      <c r="J85" s="7">
+        <f>IF(G85="","",MAX(0,(H85-G85)*24-I85/60))</f>
+        <v/>
+      </c>
+      <c r="K85" s="5" t="n"/>
       <c r="L85" s="8" t="n"/>
-      <c r="M85" s="8">
-        <f>IF(L85="","",L85*20)</f>
-        <v/>
-      </c>
-      <c r="N85" s="8" t="n"/>
+      <c r="M85" s="8" t="n"/>
+      <c r="N85" s="8">
+        <f>IF(M85="","",M85*20)</f>
+        <v/>
+      </c>
       <c r="O85" s="8" t="n"/>
-      <c r="P85" s="8">
-        <f>IF(D85="","",SUM(K85,M85,N85,O85))</f>
+      <c r="P85" s="8" t="n"/>
+      <c r="Q85" s="8">
+        <f>IF(D85="","",SUM(L85,N85,O85,P85))</f>
         <v/>
       </c>
     </row>
@@ -3127,24 +3216,25 @@
       <c r="C86" s="11" t="n"/>
       <c r="D86" s="11" t="n"/>
       <c r="E86" s="11" t="n"/>
-      <c r="F86" s="12" t="n"/>
+      <c r="F86" s="11" t="n"/>
       <c r="G86" s="12" t="n"/>
-      <c r="H86" s="11" t="n"/>
-      <c r="I86" s="13">
-        <f>IF(F86="","",MAX(0,(G86-F86)*24-H86/60))</f>
-        <v/>
-      </c>
-      <c r="J86" s="11" t="n"/>
-      <c r="K86" s="14" t="n"/>
+      <c r="H86" s="12" t="n"/>
+      <c r="I86" s="11" t="n"/>
+      <c r="J86" s="13">
+        <f>IF(G86="","",MAX(0,(H86-G86)*24-I86/60))</f>
+        <v/>
+      </c>
+      <c r="K86" s="11" t="n"/>
       <c r="L86" s="14" t="n"/>
-      <c r="M86" s="14">
-        <f>IF(L86="","",L86*20)</f>
-        <v/>
-      </c>
-      <c r="N86" s="14" t="n"/>
+      <c r="M86" s="14" t="n"/>
+      <c r="N86" s="14">
+        <f>IF(M86="","",M86*20)</f>
+        <v/>
+      </c>
       <c r="O86" s="14" t="n"/>
-      <c r="P86" s="14">
-        <f>IF(D86="","",SUM(K86,M86,N86,O86))</f>
+      <c r="P86" s="14" t="n"/>
+      <c r="Q86" s="14">
+        <f>IF(D86="","",SUM(L86,N86,O86,P86))</f>
         <v/>
       </c>
     </row>
@@ -3157,24 +3247,25 @@
       <c r="C87" s="5" t="n"/>
       <c r="D87" s="5" t="n"/>
       <c r="E87" s="5" t="n"/>
-      <c r="F87" s="6" t="n"/>
+      <c r="F87" s="5" t="n"/>
       <c r="G87" s="6" t="n"/>
-      <c r="H87" s="5" t="n"/>
-      <c r="I87" s="7">
-        <f>IF(F87="","",MAX(0,(G87-F87)*24-H87/60))</f>
-        <v/>
-      </c>
-      <c r="J87" s="5" t="n"/>
-      <c r="K87" s="8" t="n"/>
+      <c r="H87" s="6" t="n"/>
+      <c r="I87" s="5" t="n"/>
+      <c r="J87" s="7">
+        <f>IF(G87="","",MAX(0,(H87-G87)*24-I87/60))</f>
+        <v/>
+      </c>
+      <c r="K87" s="5" t="n"/>
       <c r="L87" s="8" t="n"/>
-      <c r="M87" s="8">
-        <f>IF(L87="","",L87*20)</f>
-        <v/>
-      </c>
-      <c r="N87" s="8" t="n"/>
+      <c r="M87" s="8" t="n"/>
+      <c r="N87" s="8">
+        <f>IF(M87="","",M87*20)</f>
+        <v/>
+      </c>
       <c r="O87" s="8" t="n"/>
-      <c r="P87" s="8">
-        <f>IF(D87="","",SUM(K87,M87,N87,O87))</f>
+      <c r="P87" s="8" t="n"/>
+      <c r="Q87" s="8">
+        <f>IF(D87="","",SUM(L87,N87,O87,P87))</f>
         <v/>
       </c>
     </row>
@@ -3187,24 +3278,25 @@
       <c r="C88" s="11" t="n"/>
       <c r="D88" s="11" t="n"/>
       <c r="E88" s="11" t="n"/>
-      <c r="F88" s="12" t="n"/>
+      <c r="F88" s="11" t="n"/>
       <c r="G88" s="12" t="n"/>
-      <c r="H88" s="11" t="n"/>
-      <c r="I88" s="13">
-        <f>IF(F88="","",MAX(0,(G88-F88)*24-H88/60))</f>
-        <v/>
-      </c>
-      <c r="J88" s="11" t="n"/>
-      <c r="K88" s="14" t="n"/>
+      <c r="H88" s="12" t="n"/>
+      <c r="I88" s="11" t="n"/>
+      <c r="J88" s="13">
+        <f>IF(G88="","",MAX(0,(H88-G88)*24-I88/60))</f>
+        <v/>
+      </c>
+      <c r="K88" s="11" t="n"/>
       <c r="L88" s="14" t="n"/>
-      <c r="M88" s="14">
-        <f>IF(L88="","",L88*20)</f>
-        <v/>
-      </c>
-      <c r="N88" s="14" t="n"/>
+      <c r="M88" s="14" t="n"/>
+      <c r="N88" s="14">
+        <f>IF(M88="","",M88*20)</f>
+        <v/>
+      </c>
       <c r="O88" s="14" t="n"/>
-      <c r="P88" s="14">
-        <f>IF(D88="","",SUM(K88,M88,N88,O88))</f>
+      <c r="P88" s="14" t="n"/>
+      <c r="Q88" s="14">
+        <f>IF(D88="","",SUM(L88,N88,O88,P88))</f>
         <v/>
       </c>
     </row>
@@ -3217,24 +3309,25 @@
       <c r="C89" s="5" t="n"/>
       <c r="D89" s="5" t="n"/>
       <c r="E89" s="5" t="n"/>
-      <c r="F89" s="6" t="n"/>
+      <c r="F89" s="5" t="n"/>
       <c r="G89" s="6" t="n"/>
-      <c r="H89" s="5" t="n"/>
-      <c r="I89" s="7">
-        <f>IF(F89="","",MAX(0,(G89-F89)*24-H89/60))</f>
-        <v/>
-      </c>
-      <c r="J89" s="5" t="n"/>
-      <c r="K89" s="8" t="n"/>
+      <c r="H89" s="6" t="n"/>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="7">
+        <f>IF(G89="","",MAX(0,(H89-G89)*24-I89/60))</f>
+        <v/>
+      </c>
+      <c r="K89" s="5" t="n"/>
       <c r="L89" s="8" t="n"/>
-      <c r="M89" s="8">
-        <f>IF(L89="","",L89*20)</f>
-        <v/>
-      </c>
-      <c r="N89" s="8" t="n"/>
+      <c r="M89" s="8" t="n"/>
+      <c r="N89" s="8">
+        <f>IF(M89="","",M89*20)</f>
+        <v/>
+      </c>
       <c r="O89" s="8" t="n"/>
-      <c r="P89" s="8">
-        <f>IF(D89="","",SUM(K89,M89,N89,O89))</f>
+      <c r="P89" s="8" t="n"/>
+      <c r="Q89" s="8">
+        <f>IF(D89="","",SUM(L89,N89,O89,P89))</f>
         <v/>
       </c>
     </row>
@@ -3247,24 +3340,25 @@
       <c r="C90" s="11" t="n"/>
       <c r="D90" s="11" t="n"/>
       <c r="E90" s="11" t="n"/>
-      <c r="F90" s="12" t="n"/>
+      <c r="F90" s="11" t="n"/>
       <c r="G90" s="12" t="n"/>
-      <c r="H90" s="11" t="n"/>
-      <c r="I90" s="13">
-        <f>IF(F90="","",MAX(0,(G90-F90)*24-H90/60))</f>
-        <v/>
-      </c>
-      <c r="J90" s="11" t="n"/>
-      <c r="K90" s="14" t="n"/>
+      <c r="H90" s="12" t="n"/>
+      <c r="I90" s="11" t="n"/>
+      <c r="J90" s="13">
+        <f>IF(G90="","",MAX(0,(H90-G90)*24-I90/60))</f>
+        <v/>
+      </c>
+      <c r="K90" s="11" t="n"/>
       <c r="L90" s="14" t="n"/>
-      <c r="M90" s="14">
-        <f>IF(L90="","",L90*20)</f>
-        <v/>
-      </c>
-      <c r="N90" s="14" t="n"/>
+      <c r="M90" s="14" t="n"/>
+      <c r="N90" s="14">
+        <f>IF(M90="","",M90*20)</f>
+        <v/>
+      </c>
       <c r="O90" s="14" t="n"/>
-      <c r="P90" s="14">
-        <f>IF(D90="","",SUM(K90,M90,N90,O90))</f>
+      <c r="P90" s="14" t="n"/>
+      <c r="Q90" s="14">
+        <f>IF(D90="","",SUM(L90,N90,O90,P90))</f>
         <v/>
       </c>
     </row>
@@ -3277,24 +3371,25 @@
       <c r="C91" s="5" t="n"/>
       <c r="D91" s="5" t="n"/>
       <c r="E91" s="5" t="n"/>
-      <c r="F91" s="6" t="n"/>
+      <c r="F91" s="5" t="n"/>
       <c r="G91" s="6" t="n"/>
-      <c r="H91" s="5" t="n"/>
-      <c r="I91" s="7">
-        <f>IF(F91="","",MAX(0,(G91-F91)*24-H91/60))</f>
-        <v/>
-      </c>
-      <c r="J91" s="5" t="n"/>
-      <c r="K91" s="8" t="n"/>
+      <c r="H91" s="6" t="n"/>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="7">
+        <f>IF(G91="","",MAX(0,(H91-G91)*24-I91/60))</f>
+        <v/>
+      </c>
+      <c r="K91" s="5" t="n"/>
       <c r="L91" s="8" t="n"/>
-      <c r="M91" s="8">
-        <f>IF(L91="","",L91*20)</f>
-        <v/>
-      </c>
-      <c r="N91" s="8" t="n"/>
+      <c r="M91" s="8" t="n"/>
+      <c r="N91" s="8">
+        <f>IF(M91="","",M91*20)</f>
+        <v/>
+      </c>
       <c r="O91" s="8" t="n"/>
-      <c r="P91" s="8">
-        <f>IF(D91="","",SUM(K91,M91,N91,O91))</f>
+      <c r="P91" s="8" t="n"/>
+      <c r="Q91" s="8">
+        <f>IF(D91="","",SUM(L91,N91,O91,P91))</f>
         <v/>
       </c>
     </row>
@@ -3307,24 +3402,25 @@
       <c r="C92" s="11" t="n"/>
       <c r="D92" s="11" t="n"/>
       <c r="E92" s="11" t="n"/>
-      <c r="F92" s="12" t="n"/>
+      <c r="F92" s="11" t="n"/>
       <c r="G92" s="12" t="n"/>
-      <c r="H92" s="11" t="n"/>
-      <c r="I92" s="13">
-        <f>IF(F92="","",MAX(0,(G92-F92)*24-H92/60))</f>
-        <v/>
-      </c>
-      <c r="J92" s="11" t="n"/>
-      <c r="K92" s="14" t="n"/>
+      <c r="H92" s="12" t="n"/>
+      <c r="I92" s="11" t="n"/>
+      <c r="J92" s="13">
+        <f>IF(G92="","",MAX(0,(H92-G92)*24-I92/60))</f>
+        <v/>
+      </c>
+      <c r="K92" s="11" t="n"/>
       <c r="L92" s="14" t="n"/>
-      <c r="M92" s="14">
-        <f>IF(L92="","",L92*20)</f>
-        <v/>
-      </c>
-      <c r="N92" s="14" t="n"/>
+      <c r="M92" s="14" t="n"/>
+      <c r="N92" s="14">
+        <f>IF(M92="","",M92*20)</f>
+        <v/>
+      </c>
       <c r="O92" s="14" t="n"/>
-      <c r="P92" s="14">
-        <f>IF(D92="","",SUM(K92,M92,N92,O92))</f>
+      <c r="P92" s="14" t="n"/>
+      <c r="Q92" s="14">
+        <f>IF(D92="","",SUM(L92,N92,O92,P92))</f>
         <v/>
       </c>
     </row>
@@ -3337,24 +3433,25 @@
       <c r="C93" s="5" t="n"/>
       <c r="D93" s="5" t="n"/>
       <c r="E93" s="5" t="n"/>
-      <c r="F93" s="6" t="n"/>
+      <c r="F93" s="5" t="n"/>
       <c r="G93" s="6" t="n"/>
-      <c r="H93" s="5" t="n"/>
-      <c r="I93" s="7">
-        <f>IF(F93="","",MAX(0,(G93-F93)*24-H93/60))</f>
-        <v/>
-      </c>
-      <c r="J93" s="5" t="n"/>
-      <c r="K93" s="8" t="n"/>
+      <c r="H93" s="6" t="n"/>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="7">
+        <f>IF(G93="","",MAX(0,(H93-G93)*24-I93/60))</f>
+        <v/>
+      </c>
+      <c r="K93" s="5" t="n"/>
       <c r="L93" s="8" t="n"/>
-      <c r="M93" s="8">
-        <f>IF(L93="","",L93*20)</f>
-        <v/>
-      </c>
-      <c r="N93" s="8" t="n"/>
+      <c r="M93" s="8" t="n"/>
+      <c r="N93" s="8">
+        <f>IF(M93="","",M93*20)</f>
+        <v/>
+      </c>
       <c r="O93" s="8" t="n"/>
-      <c r="P93" s="8">
-        <f>IF(D93="","",SUM(K93,M93,N93,O93))</f>
+      <c r="P93" s="8" t="n"/>
+      <c r="Q93" s="8">
+        <f>IF(D93="","",SUM(L93,N93,O93,P93))</f>
         <v/>
       </c>
     </row>
@@ -3367,24 +3464,25 @@
       <c r="C94" s="11" t="n"/>
       <c r="D94" s="11" t="n"/>
       <c r="E94" s="11" t="n"/>
-      <c r="F94" s="12" t="n"/>
+      <c r="F94" s="11" t="n"/>
       <c r="G94" s="12" t="n"/>
-      <c r="H94" s="11" t="n"/>
-      <c r="I94" s="13">
-        <f>IF(F94="","",MAX(0,(G94-F94)*24-H94/60))</f>
-        <v/>
-      </c>
-      <c r="J94" s="11" t="n"/>
-      <c r="K94" s="14" t="n"/>
+      <c r="H94" s="12" t="n"/>
+      <c r="I94" s="11" t="n"/>
+      <c r="J94" s="13">
+        <f>IF(G94="","",MAX(0,(H94-G94)*24-I94/60))</f>
+        <v/>
+      </c>
+      <c r="K94" s="11" t="n"/>
       <c r="L94" s="14" t="n"/>
-      <c r="M94" s="14">
-        <f>IF(L94="","",L94*20)</f>
-        <v/>
-      </c>
-      <c r="N94" s="14" t="n"/>
+      <c r="M94" s="14" t="n"/>
+      <c r="N94" s="14">
+        <f>IF(M94="","",M94*20)</f>
+        <v/>
+      </c>
       <c r="O94" s="14" t="n"/>
-      <c r="P94" s="14">
-        <f>IF(D94="","",SUM(K94,M94,N94,O94))</f>
+      <c r="P94" s="14" t="n"/>
+      <c r="Q94" s="14">
+        <f>IF(D94="","",SUM(L94,N94,O94,P94))</f>
         <v/>
       </c>
     </row>
@@ -3397,24 +3495,25 @@
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="5" t="n"/>
       <c r="E95" s="5" t="n"/>
-      <c r="F95" s="6" t="n"/>
+      <c r="F95" s="5" t="n"/>
       <c r="G95" s="6" t="n"/>
-      <c r="H95" s="5" t="n"/>
-      <c r="I95" s="7">
-        <f>IF(F95="","",MAX(0,(G95-F95)*24-H95/60))</f>
-        <v/>
-      </c>
-      <c r="J95" s="5" t="n"/>
-      <c r="K95" s="8" t="n"/>
+      <c r="H95" s="6" t="n"/>
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="7">
+        <f>IF(G95="","",MAX(0,(H95-G95)*24-I95/60))</f>
+        <v/>
+      </c>
+      <c r="K95" s="5" t="n"/>
       <c r="L95" s="8" t="n"/>
-      <c r="M95" s="8">
-        <f>IF(L95="","",L95*20)</f>
-        <v/>
-      </c>
-      <c r="N95" s="8" t="n"/>
+      <c r="M95" s="8" t="n"/>
+      <c r="N95" s="8">
+        <f>IF(M95="","",M95*20)</f>
+        <v/>
+      </c>
       <c r="O95" s="8" t="n"/>
-      <c r="P95" s="8">
-        <f>IF(D95="","",SUM(K95,M95,N95,O95))</f>
+      <c r="P95" s="8" t="n"/>
+      <c r="Q95" s="8">
+        <f>IF(D95="","",SUM(L95,N95,O95,P95))</f>
         <v/>
       </c>
     </row>
@@ -3427,24 +3526,25 @@
       <c r="C96" s="11" t="n"/>
       <c r="D96" s="11" t="n"/>
       <c r="E96" s="11" t="n"/>
-      <c r="F96" s="12" t="n"/>
+      <c r="F96" s="11" t="n"/>
       <c r="G96" s="12" t="n"/>
-      <c r="H96" s="11" t="n"/>
-      <c r="I96" s="13">
-        <f>IF(F96="","",MAX(0,(G96-F96)*24-H96/60))</f>
-        <v/>
-      </c>
-      <c r="J96" s="11" t="n"/>
-      <c r="K96" s="14" t="n"/>
+      <c r="H96" s="12" t="n"/>
+      <c r="I96" s="11" t="n"/>
+      <c r="J96" s="13">
+        <f>IF(G96="","",MAX(0,(H96-G96)*24-I96/60))</f>
+        <v/>
+      </c>
+      <c r="K96" s="11" t="n"/>
       <c r="L96" s="14" t="n"/>
-      <c r="M96" s="14">
-        <f>IF(L96="","",L96*20)</f>
-        <v/>
-      </c>
-      <c r="N96" s="14" t="n"/>
+      <c r="M96" s="14" t="n"/>
+      <c r="N96" s="14">
+        <f>IF(M96="","",M96*20)</f>
+        <v/>
+      </c>
       <c r="O96" s="14" t="n"/>
-      <c r="P96" s="14">
-        <f>IF(D96="","",SUM(K96,M96,N96,O96))</f>
+      <c r="P96" s="14" t="n"/>
+      <c r="Q96" s="14">
+        <f>IF(D96="","",SUM(L96,N96,O96,P96))</f>
         <v/>
       </c>
     </row>
@@ -3457,24 +3557,25 @@
       <c r="C97" s="5" t="n"/>
       <c r="D97" s="5" t="n"/>
       <c r="E97" s="5" t="n"/>
-      <c r="F97" s="6" t="n"/>
+      <c r="F97" s="5" t="n"/>
       <c r="G97" s="6" t="n"/>
-      <c r="H97" s="5" t="n"/>
-      <c r="I97" s="7">
-        <f>IF(F97="","",MAX(0,(G97-F97)*24-H97/60))</f>
-        <v/>
-      </c>
-      <c r="J97" s="5" t="n"/>
-      <c r="K97" s="8" t="n"/>
+      <c r="H97" s="6" t="n"/>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="7">
+        <f>IF(G97="","",MAX(0,(H97-G97)*24-I97/60))</f>
+        <v/>
+      </c>
+      <c r="K97" s="5" t="n"/>
       <c r="L97" s="8" t="n"/>
-      <c r="M97" s="8">
-        <f>IF(L97="","",L97*20)</f>
-        <v/>
-      </c>
-      <c r="N97" s="8" t="n"/>
+      <c r="M97" s="8" t="n"/>
+      <c r="N97" s="8">
+        <f>IF(M97="","",M97*20)</f>
+        <v/>
+      </c>
       <c r="O97" s="8" t="n"/>
-      <c r="P97" s="8">
-        <f>IF(D97="","",SUM(K97,M97,N97,O97))</f>
+      <c r="P97" s="8" t="n"/>
+      <c r="Q97" s="8">
+        <f>IF(D97="","",SUM(L97,N97,O97,P97))</f>
         <v/>
       </c>
     </row>
@@ -3487,24 +3588,25 @@
       <c r="C98" s="11" t="n"/>
       <c r="D98" s="11" t="n"/>
       <c r="E98" s="11" t="n"/>
-      <c r="F98" s="12" t="n"/>
+      <c r="F98" s="11" t="n"/>
       <c r="G98" s="12" t="n"/>
-      <c r="H98" s="11" t="n"/>
-      <c r="I98" s="13">
-        <f>IF(F98="","",MAX(0,(G98-F98)*24-H98/60))</f>
-        <v/>
-      </c>
-      <c r="J98" s="11" t="n"/>
-      <c r="K98" s="14" t="n"/>
+      <c r="H98" s="12" t="n"/>
+      <c r="I98" s="11" t="n"/>
+      <c r="J98" s="13">
+        <f>IF(G98="","",MAX(0,(H98-G98)*24-I98/60))</f>
+        <v/>
+      </c>
+      <c r="K98" s="11" t="n"/>
       <c r="L98" s="14" t="n"/>
-      <c r="M98" s="14">
-        <f>IF(L98="","",L98*20)</f>
-        <v/>
-      </c>
-      <c r="N98" s="14" t="n"/>
+      <c r="M98" s="14" t="n"/>
+      <c r="N98" s="14">
+        <f>IF(M98="","",M98*20)</f>
+        <v/>
+      </c>
       <c r="O98" s="14" t="n"/>
-      <c r="P98" s="14">
-        <f>IF(D98="","",SUM(K98,M98,N98,O98))</f>
+      <c r="P98" s="14" t="n"/>
+      <c r="Q98" s="14">
+        <f>IF(D98="","",SUM(L98,N98,O98,P98))</f>
         <v/>
       </c>
     </row>
@@ -3517,24 +3619,25 @@
       <c r="C99" s="5" t="n"/>
       <c r="D99" s="5" t="n"/>
       <c r="E99" s="5" t="n"/>
-      <c r="F99" s="6" t="n"/>
+      <c r="F99" s="5" t="n"/>
       <c r="G99" s="6" t="n"/>
-      <c r="H99" s="5" t="n"/>
-      <c r="I99" s="7">
-        <f>IF(F99="","",MAX(0,(G99-F99)*24-H99/60))</f>
-        <v/>
-      </c>
-      <c r="J99" s="5" t="n"/>
-      <c r="K99" s="8" t="n"/>
+      <c r="H99" s="6" t="n"/>
+      <c r="I99" s="5" t="n"/>
+      <c r="J99" s="7">
+        <f>IF(G99="","",MAX(0,(H99-G99)*24-I99/60))</f>
+        <v/>
+      </c>
+      <c r="K99" s="5" t="n"/>
       <c r="L99" s="8" t="n"/>
-      <c r="M99" s="8">
-        <f>IF(L99="","",L99*20)</f>
-        <v/>
-      </c>
-      <c r="N99" s="8" t="n"/>
+      <c r="M99" s="8" t="n"/>
+      <c r="N99" s="8">
+        <f>IF(M99="","",M99*20)</f>
+        <v/>
+      </c>
       <c r="O99" s="8" t="n"/>
-      <c r="P99" s="8">
-        <f>IF(D99="","",SUM(K99,M99,N99,O99))</f>
+      <c r="P99" s="8" t="n"/>
+      <c r="Q99" s="8">
+        <f>IF(D99="","",SUM(L99,N99,O99,P99))</f>
         <v/>
       </c>
     </row>
@@ -3547,24 +3650,25 @@
       <c r="C100" s="11" t="n"/>
       <c r="D100" s="11" t="n"/>
       <c r="E100" s="11" t="n"/>
-      <c r="F100" s="12" t="n"/>
+      <c r="F100" s="11" t="n"/>
       <c r="G100" s="12" t="n"/>
-      <c r="H100" s="11" t="n"/>
-      <c r="I100" s="13">
-        <f>IF(F100="","",MAX(0,(G100-F100)*24-H100/60))</f>
-        <v/>
-      </c>
-      <c r="J100" s="11" t="n"/>
-      <c r="K100" s="14" t="n"/>
+      <c r="H100" s="12" t="n"/>
+      <c r="I100" s="11" t="n"/>
+      <c r="J100" s="13">
+        <f>IF(G100="","",MAX(0,(H100-G100)*24-I100/60))</f>
+        <v/>
+      </c>
+      <c r="K100" s="11" t="n"/>
       <c r="L100" s="14" t="n"/>
-      <c r="M100" s="14">
-        <f>IF(L100="","",L100*20)</f>
-        <v/>
-      </c>
-      <c r="N100" s="14" t="n"/>
+      <c r="M100" s="14" t="n"/>
+      <c r="N100" s="14">
+        <f>IF(M100="","",M100*20)</f>
+        <v/>
+      </c>
       <c r="O100" s="14" t="n"/>
-      <c r="P100" s="14">
-        <f>IF(D100="","",SUM(K100,M100,N100,O100))</f>
+      <c r="P100" s="14" t="n"/>
+      <c r="Q100" s="14">
+        <f>IF(D100="","",SUM(L100,N100,O100,P100))</f>
         <v/>
       </c>
     </row>
@@ -3577,24 +3681,25 @@
       <c r="C101" s="5" t="n"/>
       <c r="D101" s="5" t="n"/>
       <c r="E101" s="5" t="n"/>
-      <c r="F101" s="6" t="n"/>
+      <c r="F101" s="5" t="n"/>
       <c r="G101" s="6" t="n"/>
-      <c r="H101" s="5" t="n"/>
-      <c r="I101" s="7">
-        <f>IF(F101="","",MAX(0,(G101-F101)*24-H101/60))</f>
-        <v/>
-      </c>
-      <c r="J101" s="5" t="n"/>
-      <c r="K101" s="8" t="n"/>
+      <c r="H101" s="6" t="n"/>
+      <c r="I101" s="5" t="n"/>
+      <c r="J101" s="7">
+        <f>IF(G101="","",MAX(0,(H101-G101)*24-I101/60))</f>
+        <v/>
+      </c>
+      <c r="K101" s="5" t="n"/>
       <c r="L101" s="8" t="n"/>
-      <c r="M101" s="8">
-        <f>IF(L101="","",L101*20)</f>
-        <v/>
-      </c>
-      <c r="N101" s="8" t="n"/>
+      <c r="M101" s="8" t="n"/>
+      <c r="N101" s="8">
+        <f>IF(M101="","",M101*20)</f>
+        <v/>
+      </c>
       <c r="O101" s="8" t="n"/>
-      <c r="P101" s="8">
-        <f>IF(D101="","",SUM(K101,M101,N101,O101))</f>
+      <c r="P101" s="8" t="n"/>
+      <c r="Q101" s="8">
+        <f>IF(D101="","",SUM(L101,N101,O101,P101))</f>
         <v/>
       </c>
     </row>
@@ -3607,24 +3712,25 @@
       <c r="C102" s="11" t="n"/>
       <c r="D102" s="11" t="n"/>
       <c r="E102" s="11" t="n"/>
-      <c r="F102" s="12" t="n"/>
+      <c r="F102" s="11" t="n"/>
       <c r="G102" s="12" t="n"/>
-      <c r="H102" s="11" t="n"/>
-      <c r="I102" s="13">
-        <f>IF(F102="","",MAX(0,(G102-F102)*24-H102/60))</f>
-        <v/>
-      </c>
-      <c r="J102" s="11" t="n"/>
-      <c r="K102" s="14" t="n"/>
+      <c r="H102" s="12" t="n"/>
+      <c r="I102" s="11" t="n"/>
+      <c r="J102" s="13">
+        <f>IF(G102="","",MAX(0,(H102-G102)*24-I102/60))</f>
+        <v/>
+      </c>
+      <c r="K102" s="11" t="n"/>
       <c r="L102" s="14" t="n"/>
-      <c r="M102" s="14">
-        <f>IF(L102="","",L102*20)</f>
-        <v/>
-      </c>
-      <c r="N102" s="14" t="n"/>
+      <c r="M102" s="14" t="n"/>
+      <c r="N102" s="14">
+        <f>IF(M102="","",M102*20)</f>
+        <v/>
+      </c>
       <c r="O102" s="14" t="n"/>
-      <c r="P102" s="14">
-        <f>IF(D102="","",SUM(K102,M102,N102,O102))</f>
+      <c r="P102" s="14" t="n"/>
+      <c r="Q102" s="14">
+        <f>IF(D102="","",SUM(L102,N102,O102,P102))</f>
         <v/>
       </c>
     </row>
@@ -3641,20 +3747,17 @@
       <c r="F103" s="16" t="n"/>
       <c r="G103" s="16" t="n"/>
       <c r="H103" s="16" t="n"/>
-      <c r="I103" s="15">
+      <c r="I103" s="16" t="n"/>
+      <c r="J103" s="15">
         <f>COUNTA(B3:B102)</f>
         <v/>
       </c>
-      <c r="J103" s="16" t="n"/>
-      <c r="K103" s="17">
-        <f>SUM(K3:K102)</f>
-        <v/>
-      </c>
-      <c r="L103" s="16" t="n"/>
-      <c r="M103" s="17">
-        <f>SUM(M3:M102)</f>
-        <v/>
-      </c>
+      <c r="K103" s="16" t="n"/>
+      <c r="L103" s="17">
+        <f>SUM(L3:L102)</f>
+        <v/>
+      </c>
+      <c r="M103" s="16" t="n"/>
       <c r="N103" s="17">
         <f>SUM(N3:N102)</f>
         <v/>
@@ -3667,11 +3770,15 @@
         <f>SUM(P3:P102)</f>
         <v/>
       </c>
+      <c r="Q103" s="17">
+        <f>SUM(Q3:Q102)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P102"/>
+  <autoFilter ref="A2:Q102"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A103:B103"/>
   </mergeCells>
   <dataValidations count="2">
